--- a/Code/Jupiter/Connect4/Logs/PPO/PPO-4000-CUR-Finale_B-PPO_402 - at-2026-01-20 18-36-53-benchmark.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO/PPO-4000-CUR-Finale_B-PPO_402 - at-2026-01-20 18-36-53-benchmark.xlsx
@@ -419,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P90"/>
+  <dimension ref="A1:P113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -4655,6 +4655,1087 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="91" spans="1:16">
+      <c r="A91">
+        <v>1780</v>
+      </c>
+      <c r="B91">
+        <v>0.4107185</v>
+      </c>
+      <c r="C91">
+        <v>0.745</v>
+      </c>
+      <c r="D91">
+        <v>0.74</v>
+      </c>
+      <c r="E91">
+        <v>0.6324016497895343</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91">
+        <v>0.99</v>
+      </c>
+      <c r="I91">
+        <v>0.22</v>
+      </c>
+      <c r="J91">
+        <v>0.5</v>
+      </c>
+      <c r="K91">
+        <v>0.5</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="M91">
+        <v>0.5</v>
+      </c>
+      <c r="N91">
+        <v>0.5</v>
+      </c>
+      <c r="O91">
+        <v>1</v>
+      </c>
+      <c r="P91">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16">
+      <c r="A92">
+        <v>1800</v>
+      </c>
+      <c r="B92">
+        <v>0.4107185</v>
+      </c>
+      <c r="C92">
+        <v>0.745</v>
+      </c>
+      <c r="D92">
+        <v>0.74</v>
+      </c>
+      <c r="E92">
+        <v>0.6323289961917612</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+      <c r="H92">
+        <v>1</v>
+      </c>
+      <c r="I92">
+        <v>0.21</v>
+      </c>
+      <c r="J92">
+        <v>0.5</v>
+      </c>
+      <c r="K92">
+        <v>0.5</v>
+      </c>
+      <c r="L92">
+        <v>1</v>
+      </c>
+      <c r="M92">
+        <v>0.5</v>
+      </c>
+      <c r="N92">
+        <v>0.5</v>
+      </c>
+      <c r="O92">
+        <v>1</v>
+      </c>
+      <c r="P92">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16">
+      <c r="A93">
+        <v>1820</v>
+      </c>
+      <c r="B93">
+        <v>0.4107185</v>
+      </c>
+      <c r="C93">
+        <v>0.745</v>
+      </c>
+      <c r="D93">
+        <v>0.74</v>
+      </c>
+      <c r="E93">
+        <v>0.6320565452001119</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
+      <c r="H93">
+        <v>0.985</v>
+      </c>
+      <c r="I93">
+        <v>0.21</v>
+      </c>
+      <c r="J93">
+        <v>0.5</v>
+      </c>
+      <c r="K93">
+        <v>0.5</v>
+      </c>
+      <c r="L93">
+        <v>1</v>
+      </c>
+      <c r="M93">
+        <v>0.5</v>
+      </c>
+      <c r="N93">
+        <v>0.5</v>
+      </c>
+      <c r="O93">
+        <v>1</v>
+      </c>
+      <c r="P93">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16">
+      <c r="A94">
+        <v>1840</v>
+      </c>
+      <c r="B94">
+        <v>0.4107185</v>
+      </c>
+      <c r="C94">
+        <v>0.745</v>
+      </c>
+      <c r="D94">
+        <v>0.74</v>
+      </c>
+      <c r="E94">
+        <v>0.635035342708811</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+      <c r="H94">
+        <v>0.995</v>
+      </c>
+      <c r="I94">
+        <v>0.32</v>
+      </c>
+      <c r="J94">
+        <v>0.5</v>
+      </c>
+      <c r="K94">
+        <v>0.5</v>
+      </c>
+      <c r="L94">
+        <v>1</v>
+      </c>
+      <c r="M94">
+        <v>0.5</v>
+      </c>
+      <c r="N94">
+        <v>0.5</v>
+      </c>
+      <c r="O94">
+        <v>1</v>
+      </c>
+      <c r="P94">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16">
+      <c r="A95">
+        <v>1860</v>
+      </c>
+      <c r="B95">
+        <v>0.4107185</v>
+      </c>
+      <c r="C95">
+        <v>0.745</v>
+      </c>
+      <c r="D95">
+        <v>0.74</v>
+      </c>
+      <c r="E95">
+        <v>0.6332553295633688</v>
+      </c>
+      <c r="G95">
+        <v>1</v>
+      </c>
+      <c r="H95">
+        <v>0.995</v>
+      </c>
+      <c r="I95">
+        <v>0.25</v>
+      </c>
+      <c r="J95">
+        <v>0.5</v>
+      </c>
+      <c r="K95">
+        <v>0.5</v>
+      </c>
+      <c r="L95">
+        <v>1</v>
+      </c>
+      <c r="M95">
+        <v>0.5</v>
+      </c>
+      <c r="N95">
+        <v>0.5</v>
+      </c>
+      <c r="O95">
+        <v>1</v>
+      </c>
+      <c r="P95">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16">
+      <c r="A96">
+        <v>1880</v>
+      </c>
+      <c r="B96">
+        <v>0.4107185</v>
+      </c>
+      <c r="C96">
+        <v>0.745</v>
+      </c>
+      <c r="D96">
+        <v>0.74</v>
+      </c>
+      <c r="E96">
+        <v>0.6335822707533481</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+      <c r="H96">
+        <v>0.985</v>
+      </c>
+      <c r="I96">
+        <v>0.27</v>
+      </c>
+      <c r="J96">
+        <v>0.5</v>
+      </c>
+      <c r="K96">
+        <v>0.5</v>
+      </c>
+      <c r="L96">
+        <v>1</v>
+      </c>
+      <c r="M96">
+        <v>0.5</v>
+      </c>
+      <c r="N96">
+        <v>0.5</v>
+      </c>
+      <c r="O96">
+        <v>1</v>
+      </c>
+      <c r="P96">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16">
+      <c r="A97">
+        <v>1900</v>
+      </c>
+      <c r="B97">
+        <v>0.4107185</v>
+      </c>
+      <c r="C97">
+        <v>0.745</v>
+      </c>
+      <c r="D97">
+        <v>0.74</v>
+      </c>
+      <c r="E97">
+        <v>0.6204731399284796</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+      <c r="H97">
+        <v>0.995</v>
+      </c>
+      <c r="I97">
+        <v>0.27</v>
+      </c>
+      <c r="J97">
+        <v>0.5</v>
+      </c>
+      <c r="K97">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="L97">
+        <v>1</v>
+      </c>
+      <c r="M97">
+        <v>0.5</v>
+      </c>
+      <c r="N97">
+        <v>0.5</v>
+      </c>
+      <c r="O97">
+        <v>1</v>
+      </c>
+      <c r="P97">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16">
+      <c r="A98">
+        <v>1920</v>
+      </c>
+      <c r="B98">
+        <v>0.4107185</v>
+      </c>
+      <c r="C98">
+        <v>0.745</v>
+      </c>
+      <c r="D98">
+        <v>0.74</v>
+      </c>
+      <c r="E98">
+        <v>0.6237498171880487</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+      <c r="H98">
+        <v>0.985</v>
+      </c>
+      <c r="I98">
+        <v>0.21</v>
+      </c>
+      <c r="J98">
+        <v>0.5</v>
+      </c>
+      <c r="K98">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="L98">
+        <v>1</v>
+      </c>
+      <c r="M98">
+        <v>0.5</v>
+      </c>
+      <c r="N98">
+        <v>0.5</v>
+      </c>
+      <c r="O98">
+        <v>1</v>
+      </c>
+      <c r="P98">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16">
+      <c r="A99">
+        <v>1940</v>
+      </c>
+      <c r="B99">
+        <v>0.4107185</v>
+      </c>
+      <c r="C99">
+        <v>0.745</v>
+      </c>
+      <c r="D99">
+        <v>0.74</v>
+      </c>
+      <c r="E99">
+        <v>0.6172412657208708</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+      <c r="H99">
+        <v>1</v>
+      </c>
+      <c r="I99">
+        <v>0.27</v>
+      </c>
+      <c r="J99">
+        <v>0.5</v>
+      </c>
+      <c r="K99">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="L99">
+        <v>1</v>
+      </c>
+      <c r="M99">
+        <v>0.5</v>
+      </c>
+      <c r="N99">
+        <v>0.5</v>
+      </c>
+      <c r="O99">
+        <v>1</v>
+      </c>
+      <c r="P99">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16">
+      <c r="A100">
+        <v>1960</v>
+      </c>
+      <c r="B100">
+        <v>0.4107185</v>
+      </c>
+      <c r="C100">
+        <v>0.745</v>
+      </c>
+      <c r="D100">
+        <v>0.74</v>
+      </c>
+      <c r="E100">
+        <v>0.6226878637672645</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+      <c r="H100">
+        <v>0.99</v>
+      </c>
+      <c r="I100">
+        <v>0.23</v>
+      </c>
+      <c r="J100">
+        <v>0.5</v>
+      </c>
+      <c r="K100">
+        <v>0.3</v>
+      </c>
+      <c r="L100">
+        <v>1</v>
+      </c>
+      <c r="M100">
+        <v>0.5</v>
+      </c>
+      <c r="N100">
+        <v>0.5</v>
+      </c>
+      <c r="O100">
+        <v>1</v>
+      </c>
+      <c r="P100">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16">
+      <c r="A101">
+        <v>1980</v>
+      </c>
+      <c r="B101">
+        <v>0.4107185</v>
+      </c>
+      <c r="C101">
+        <v>0.745</v>
+      </c>
+      <c r="D101">
+        <v>0.74</v>
+      </c>
+      <c r="E101">
+        <v>0.6192017019674496</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="H101">
+        <v>0.995</v>
+      </c>
+      <c r="I101">
+        <v>0.22</v>
+      </c>
+      <c r="J101">
+        <v>0.5</v>
+      </c>
+      <c r="K101">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="L101">
+        <v>1</v>
+      </c>
+      <c r="M101">
+        <v>0.5</v>
+      </c>
+      <c r="N101">
+        <v>0.5</v>
+      </c>
+      <c r="O101">
+        <v>1</v>
+      </c>
+      <c r="P101">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16">
+      <c r="A102">
+        <v>2000</v>
+      </c>
+      <c r="B102">
+        <v>0.407943375</v>
+      </c>
+      <c r="C102">
+        <v>0.745</v>
+      </c>
+      <c r="D102">
+        <v>0.735</v>
+      </c>
+      <c r="E102">
+        <v>0.6215350933492638</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>0.99</v>
+      </c>
+      <c r="I102">
+        <v>0.25</v>
+      </c>
+      <c r="J102">
+        <v>0.5</v>
+      </c>
+      <c r="K102">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="L102">
+        <v>1</v>
+      </c>
+      <c r="M102">
+        <v>0.5</v>
+      </c>
+      <c r="N102">
+        <v>0.5</v>
+      </c>
+      <c r="O102">
+        <v>1</v>
+      </c>
+      <c r="P102">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16">
+      <c r="A103">
+        <v>2020</v>
+      </c>
+      <c r="B103">
+        <v>0.407943375</v>
+      </c>
+      <c r="C103">
+        <v>0.745</v>
+      </c>
+      <c r="D103">
+        <v>0.735</v>
+      </c>
+      <c r="E103">
+        <v>0.6202006889368304</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="H103">
+        <v>0.98</v>
+      </c>
+      <c r="I103">
+        <v>0.27</v>
+      </c>
+      <c r="J103">
+        <v>0.5</v>
+      </c>
+      <c r="K103">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="L103">
+        <v>1</v>
+      </c>
+      <c r="M103">
+        <v>0.5</v>
+      </c>
+      <c r="N103">
+        <v>0.5</v>
+      </c>
+      <c r="O103">
+        <v>1</v>
+      </c>
+      <c r="P103">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16">
+      <c r="A104">
+        <v>2040</v>
+      </c>
+      <c r="B104">
+        <v>0.407943375</v>
+      </c>
+      <c r="C104">
+        <v>0.745</v>
+      </c>
+      <c r="D104">
+        <v>0.735</v>
+      </c>
+      <c r="E104">
+        <v>0.6178672975550161</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="H104">
+        <v>0.985</v>
+      </c>
+      <c r="I104">
+        <v>0.24</v>
+      </c>
+      <c r="J104">
+        <v>0.5</v>
+      </c>
+      <c r="K104">
+        <v>0.2</v>
+      </c>
+      <c r="L104">
+        <v>1</v>
+      </c>
+      <c r="M104">
+        <v>0.5</v>
+      </c>
+      <c r="N104">
+        <v>0.5</v>
+      </c>
+      <c r="O104">
+        <v>1</v>
+      </c>
+      <c r="P104">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16">
+      <c r="A105">
+        <v>2060</v>
+      </c>
+      <c r="B105">
+        <v>0.407943375</v>
+      </c>
+      <c r="C105">
+        <v>0.745</v>
+      </c>
+      <c r="D105">
+        <v>0.735</v>
+      </c>
+      <c r="E105">
+        <v>0.6147988939423968</v>
+      </c>
+      <c r="G105">
+        <v>1</v>
+      </c>
+      <c r="H105">
+        <v>0.985</v>
+      </c>
+      <c r="I105">
+        <v>0.25</v>
+      </c>
+      <c r="J105">
+        <v>0.5</v>
+      </c>
+      <c r="K105">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="L105">
+        <v>1</v>
+      </c>
+      <c r="M105">
+        <v>0.5</v>
+      </c>
+      <c r="N105">
+        <v>0.5</v>
+      </c>
+      <c r="O105">
+        <v>1</v>
+      </c>
+      <c r="P105">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16">
+      <c r="A106">
+        <v>2080</v>
+      </c>
+      <c r="B106">
+        <v>0.407943375</v>
+      </c>
+      <c r="C106">
+        <v>0.745</v>
+      </c>
+      <c r="D106">
+        <v>0.735</v>
+      </c>
+      <c r="E106">
+        <v>0.6247669675568727</v>
+      </c>
+      <c r="G106">
+        <v>1</v>
+      </c>
+      <c r="H106">
+        <v>0.985</v>
+      </c>
+      <c r="I106">
+        <v>0.25</v>
+      </c>
+      <c r="J106">
+        <v>0.5</v>
+      </c>
+      <c r="K106">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="L106">
+        <v>1</v>
+      </c>
+      <c r="M106">
+        <v>0.5</v>
+      </c>
+      <c r="N106">
+        <v>0.5</v>
+      </c>
+      <c r="O106">
+        <v>1</v>
+      </c>
+      <c r="P106">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16">
+      <c r="A107">
+        <v>2100</v>
+      </c>
+      <c r="B107">
+        <v>0.407943375</v>
+      </c>
+      <c r="C107">
+        <v>0.745</v>
+      </c>
+      <c r="D107">
+        <v>0.735</v>
+      </c>
+      <c r="E107">
+        <v>0.6174773899136335</v>
+      </c>
+      <c r="G107">
+        <v>1</v>
+      </c>
+      <c r="H107">
+        <v>0.985</v>
+      </c>
+      <c r="I107">
+        <v>0.29</v>
+      </c>
+      <c r="J107">
+        <v>0.5</v>
+      </c>
+      <c r="K107">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="L107">
+        <v>1</v>
+      </c>
+      <c r="M107">
+        <v>0.5</v>
+      </c>
+      <c r="N107">
+        <v>0.5</v>
+      </c>
+      <c r="O107">
+        <v>1</v>
+      </c>
+      <c r="P107">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16">
+      <c r="A108">
+        <v>2120</v>
+      </c>
+      <c r="B108">
+        <v>0.4079666250000001</v>
+      </c>
+      <c r="C108">
+        <v>0.7425</v>
+      </c>
+      <c r="D108">
+        <v>0.74</v>
+      </c>
+      <c r="E108">
+        <v>0.6203544723854502</v>
+      </c>
+      <c r="G108">
+        <v>1</v>
+      </c>
+      <c r="H108">
+        <v>0.995</v>
+      </c>
+      <c r="I108">
+        <v>0.2</v>
+      </c>
+      <c r="J108">
+        <v>0.5</v>
+      </c>
+      <c r="K108">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="L108">
+        <v>1</v>
+      </c>
+      <c r="M108">
+        <v>0.5</v>
+      </c>
+      <c r="N108">
+        <v>0.5</v>
+      </c>
+      <c r="O108">
+        <v>1</v>
+      </c>
+      <c r="P108">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16">
+      <c r="A109">
+        <v>2140</v>
+      </c>
+      <c r="B109">
+        <v>0.4079666250000001</v>
+      </c>
+      <c r="C109">
+        <v>0.7425</v>
+      </c>
+      <c r="D109">
+        <v>0.74</v>
+      </c>
+      <c r="E109">
+        <v>0.6162967689498199</v>
+      </c>
+      <c r="G109">
+        <v>1</v>
+      </c>
+      <c r="H109">
+        <v>0.99</v>
+      </c>
+      <c r="I109">
+        <v>0.24</v>
+      </c>
+      <c r="J109">
+        <v>0.5</v>
+      </c>
+      <c r="K109">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="L109">
+        <v>1</v>
+      </c>
+      <c r="M109">
+        <v>0.5</v>
+      </c>
+      <c r="N109">
+        <v>0.5</v>
+      </c>
+      <c r="O109">
+        <v>1</v>
+      </c>
+      <c r="P109">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16">
+      <c r="A110">
+        <v>2160</v>
+      </c>
+      <c r="B110">
+        <v>0.4079666250000001</v>
+      </c>
+      <c r="C110">
+        <v>0.7425</v>
+      </c>
+      <c r="D110">
+        <v>0.74</v>
+      </c>
+      <c r="E110">
+        <v>0.8047600210049572</v>
+      </c>
+      <c r="G110">
+        <v>1</v>
+      </c>
+      <c r="H110">
+        <v>1</v>
+      </c>
+      <c r="I110">
+        <v>0.2</v>
+      </c>
+      <c r="J110">
+        <v>0.5</v>
+      </c>
+      <c r="K110">
+        <v>0.2</v>
+      </c>
+      <c r="L110">
+        <v>1</v>
+      </c>
+      <c r="M110">
+        <v>0.5</v>
+      </c>
+      <c r="N110">
+        <v>0.5</v>
+      </c>
+      <c r="O110">
+        <v>1</v>
+      </c>
+      <c r="P110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16">
+      <c r="A111">
+        <v>2180</v>
+      </c>
+      <c r="B111">
+        <v>0.4079666250000001</v>
+      </c>
+      <c r="C111">
+        <v>0.7425</v>
+      </c>
+      <c r="D111">
+        <v>0.74</v>
+      </c>
+      <c r="E111">
+        <v>0.8095902743635753</v>
+      </c>
+      <c r="G111">
+        <v>1</v>
+      </c>
+      <c r="H111">
+        <v>0.985</v>
+      </c>
+      <c r="I111">
+        <v>0.27</v>
+      </c>
+      <c r="J111">
+        <v>0.5</v>
+      </c>
+      <c r="K111">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="L111">
+        <v>1</v>
+      </c>
+      <c r="M111">
+        <v>0.5</v>
+      </c>
+      <c r="N111">
+        <v>0.5</v>
+      </c>
+      <c r="O111">
+        <v>1</v>
+      </c>
+      <c r="P111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16">
+      <c r="A112">
+        <v>2200</v>
+      </c>
+      <c r="B112">
+        <v>0.4079666250000001</v>
+      </c>
+      <c r="C112">
+        <v>0.7425</v>
+      </c>
+      <c r="D112">
+        <v>0.74</v>
+      </c>
+      <c r="E112">
+        <v>0.8122869337342552</v>
+      </c>
+      <c r="G112">
+        <v>1</v>
+      </c>
+      <c r="H112">
+        <v>1</v>
+      </c>
+      <c r="I112">
+        <v>0.3</v>
+      </c>
+      <c r="J112">
+        <v>0.5</v>
+      </c>
+      <c r="K112">
+        <v>0.3</v>
+      </c>
+      <c r="L112">
+        <v>1</v>
+      </c>
+      <c r="M112">
+        <v>0.5</v>
+      </c>
+      <c r="N112">
+        <v>0.5</v>
+      </c>
+      <c r="O112">
+        <v>1</v>
+      </c>
+      <c r="P112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16">
+      <c r="A113">
+        <v>2220</v>
+      </c>
+      <c r="B113">
+        <v>0.4079666250000001</v>
+      </c>
+      <c r="C113">
+        <v>0.7425</v>
+      </c>
+      <c r="D113">
+        <v>0.74</v>
+      </c>
+      <c r="E113">
+        <v>0.8035164335897401</v>
+      </c>
+      <c r="G113">
+        <v>1</v>
+      </c>
+      <c r="H113">
+        <v>0.995</v>
+      </c>
+      <c r="I113">
+        <v>0.22</v>
+      </c>
+      <c r="J113">
+        <v>0.5</v>
+      </c>
+      <c r="K113">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="L113">
+        <v>1</v>
+      </c>
+      <c r="M113">
+        <v>0.5</v>
+      </c>
+      <c r="N113">
+        <v>0.5</v>
+      </c>
+      <c r="O113">
+        <v>1</v>
+      </c>
+      <c r="P113">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Code/Jupiter/Connect4/Logs/PPO/PPO-4000-CUR-Finale_B-PPO_402 - at-2026-01-20 18-36-53-benchmark.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO/PPO-4000-CUR-Finale_B-PPO_402 - at-2026-01-20 18-36-53-benchmark.xlsx
@@ -419,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P113"/>
+  <dimension ref="A1:P162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -474,31 +474,31 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2">
-        <v>1</v>
+        <v>2920</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.413493625</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>0.745</v>
       </c>
       <c r="D2">
-        <v>0.26</v>
+        <v>0.745</v>
       </c>
       <c r="E2">
-        <v>0.6514005656072125</v>
+        <v>0.822491131541494</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0.985</v>
       </c>
       <c r="I2">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K2">
         <v>0.5</v>
@@ -516,36 +516,36 @@
         <v>1</v>
       </c>
       <c r="P2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3">
-        <v>20</v>
+        <v>2840</v>
       </c>
       <c r="B3">
-        <v>0.065</v>
+        <v>0.413493625</v>
       </c>
       <c r="C3">
-        <v>0.5</v>
+        <v>0.745</v>
       </c>
       <c r="D3">
-        <v>0.26</v>
+        <v>0.745</v>
       </c>
       <c r="E3">
-        <v>0.6501291276461824</v>
+        <v>0.8183498764684251</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.995</v>
       </c>
       <c r="I3">
-        <v>0.21</v>
+        <v>0.29</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="K3">
         <v>0.5</v>
@@ -563,24 +563,24 @@
         <v>1</v>
       </c>
       <c r="P3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4">
-        <v>40</v>
+        <v>2760</v>
       </c>
       <c r="B4">
-        <v>0.065</v>
+        <v>0.413493625</v>
       </c>
       <c r="C4">
-        <v>0.5</v>
+        <v>0.745</v>
       </c>
       <c r="D4">
-        <v>0.26</v>
+        <v>0.745</v>
       </c>
       <c r="E4">
-        <v>0.650801173425584</v>
+        <v>0.817587013691807</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -589,10 +589,10 @@
         <v>0.995</v>
       </c>
       <c r="I4">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="K4">
         <v>0.5</v>
@@ -610,24 +610,24 @@
         <v>1</v>
       </c>
       <c r="P4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5">
-        <v>60</v>
+        <v>3060</v>
       </c>
       <c r="B5">
-        <v>0.065</v>
+        <v>0.413493625</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.745</v>
       </c>
       <c r="D5">
-        <v>0.26</v>
+        <v>0.745</v>
       </c>
       <c r="E5">
-        <v>0.6509646440205735</v>
+        <v>0.81622475873356</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -636,10 +636,10 @@
         <v>0.99</v>
       </c>
       <c r="I5">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="K5">
         <v>0.5</v>
@@ -657,36 +657,36 @@
         <v>1</v>
       </c>
       <c r="P5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6">
-        <v>80</v>
+        <v>2780</v>
       </c>
       <c r="B6">
-        <v>0.065</v>
+        <v>0.413493625</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.745</v>
       </c>
       <c r="D6">
-        <v>0.26</v>
+        <v>0.745</v>
       </c>
       <c r="E6">
-        <v>0.6506195394311511</v>
+        <v>0.815788837146921</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>0.985</v>
+        <v>0.98</v>
       </c>
       <c r="I6">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="K6">
         <v>0.5</v>
@@ -704,39 +704,39 @@
         <v>1</v>
       </c>
       <c r="P6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7">
-        <v>100</v>
+        <v>2400</v>
       </c>
       <c r="B7">
-        <v>0.06625</v>
+        <v>0.407966625</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.7425</v>
       </c>
       <c r="D7">
-        <v>0.265</v>
+        <v>0.74</v>
       </c>
       <c r="E7">
-        <v>0.6333279831611419</v>
+        <v>0.815427990944648</v>
       </c>
       <c r="G7">
         <v>1</v>
       </c>
       <c r="H7">
-        <v>0.985</v>
+        <v>0.99</v>
       </c>
       <c r="I7">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="J7">
         <v>0.5</v>
       </c>
       <c r="K7">
-        <v>0.5</v>
+        <v>0.366666666666667</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -751,36 +751,36 @@
         <v>1</v>
       </c>
       <c r="P7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8">
-        <v>120</v>
+        <v>2800</v>
       </c>
       <c r="B8">
-        <v>0.06625</v>
+        <v>0.413493625</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.745</v>
       </c>
       <c r="D8">
-        <v>0.265</v>
+        <v>0.745</v>
       </c>
       <c r="E8">
-        <v>0.6325651203845238</v>
+        <v>0.813427595219294</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8">
-        <v>0.985</v>
+        <v>0.99</v>
       </c>
       <c r="I8">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="J8">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K8">
         <v>0.5</v>
@@ -798,36 +798,36 @@
         <v>1</v>
       </c>
       <c r="P8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9">
-        <v>140</v>
+        <v>3040</v>
       </c>
       <c r="B9">
-        <v>0.06625</v>
+        <v>0.413493625</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.745</v>
       </c>
       <c r="D9">
-        <v>0.265</v>
+        <v>0.745</v>
       </c>
       <c r="E9">
-        <v>0.6326559373817404</v>
+        <v>0.813336778222077</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9">
-        <v>0.99</v>
+        <v>0.985</v>
       </c>
       <c r="I9">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="J9">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K9">
         <v>0.5</v>
@@ -845,39 +845,39 @@
         <v>1</v>
       </c>
       <c r="P9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10">
-        <v>160</v>
+        <v>2200</v>
       </c>
       <c r="B10">
-        <v>0.06625</v>
+        <v>0.407966625</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0.7425</v>
       </c>
       <c r="D10">
-        <v>0.265</v>
+        <v>0.74</v>
       </c>
       <c r="E10">
-        <v>0.6330010419711628</v>
+        <v>0.812286933734255</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="J10">
         <v>0.5</v>
       </c>
       <c r="K10">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L10">
         <v>1</v>
@@ -892,39 +892,39 @@
         <v>1</v>
       </c>
       <c r="P10">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11">
-        <v>180</v>
+        <v>2240</v>
       </c>
       <c r="B11">
-        <v>0.06625</v>
+        <v>0.407966625</v>
       </c>
       <c r="C11">
-        <v>0.5</v>
+        <v>0.7425</v>
       </c>
       <c r="D11">
-        <v>0.265</v>
+        <v>0.74</v>
       </c>
       <c r="E11">
-        <v>0.6342724799321929</v>
+        <v>0.81196846879735</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11">
-        <v>0.995</v>
+        <v>0.975</v>
       </c>
       <c r="I11">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="J11">
         <v>0.5</v>
       </c>
       <c r="K11">
-        <v>0.5</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -939,36 +939,36 @@
         <v>1</v>
       </c>
       <c r="P11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12">
-        <v>200</v>
+        <v>2880</v>
       </c>
       <c r="B12">
-        <v>0.06625</v>
+        <v>0.413493625</v>
       </c>
       <c r="C12">
-        <v>0.5</v>
+        <v>0.745</v>
       </c>
       <c r="D12">
-        <v>0.265</v>
+        <v>0.745</v>
       </c>
       <c r="E12">
-        <v>0.6323108327923179</v>
+        <v>0.811647582073852</v>
       </c>
       <c r="G12">
         <v>1</v>
       </c>
       <c r="H12">
-        <v>0.985</v>
+        <v>0.99</v>
       </c>
       <c r="I12">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="J12">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="K12">
         <v>0.5</v>
@@ -986,36 +986,36 @@
         <v>1</v>
       </c>
       <c r="P12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13">
-        <v>220</v>
+        <v>2820</v>
       </c>
       <c r="B13">
-        <v>0.06625</v>
+        <v>0.413493625</v>
       </c>
       <c r="C13">
-        <v>0.5</v>
+        <v>0.745</v>
       </c>
       <c r="D13">
-        <v>0.265</v>
+        <v>0.745</v>
       </c>
       <c r="E13">
-        <v>0.6330736955689359</v>
+        <v>0.810121856520616</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13">
-        <v>0.985</v>
+        <v>0.99</v>
       </c>
       <c r="I13">
         <v>0.25</v>
       </c>
       <c r="J13">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="K13">
         <v>0.5</v>
@@ -1033,37 +1033,37 @@
         <v>1</v>
       </c>
       <c r="P13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14">
-        <v>240</v>
+        <v>2940</v>
       </c>
       <c r="B14">
-        <v>0.06625</v>
+        <v>0.413493625</v>
       </c>
       <c r="C14">
-        <v>0.5</v>
+        <v>0.745</v>
       </c>
       <c r="D14">
-        <v>0.265</v>
+        <v>0.745</v>
       </c>
       <c r="E14">
-        <v>0.6318930746051223</v>
+        <v>0.809776751931193</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14">
-        <v>0.99</v>
+        <v>0.985</v>
       </c>
       <c r="I14">
+        <v>0.24</v>
+      </c>
+      <c r="J14">
         <v>0.2</v>
       </c>
-      <c r="J14">
-        <v>0.5</v>
-      </c>
       <c r="K14">
         <v>0.5</v>
       </c>
@@ -1080,39 +1080,39 @@
         <v>1</v>
       </c>
       <c r="P14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15">
-        <v>260</v>
+        <v>2180</v>
       </c>
       <c r="B15">
-        <v>0.145114</v>
+        <v>0.407966625</v>
       </c>
       <c r="C15">
+        <v>0.7425</v>
+      </c>
+      <c r="D15">
         <v>0.74</v>
       </c>
-      <c r="D15">
-        <v>0.265</v>
-      </c>
       <c r="E15">
-        <v>0.6319838916023388</v>
+        <v>0.809590274363575</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15">
-        <v>0.995</v>
+        <v>0.985</v>
       </c>
       <c r="I15">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="J15">
         <v>0.5</v>
       </c>
       <c r="K15">
-        <v>0.5</v>
+        <v>0.266666666666667</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -1127,36 +1127,36 @@
         <v>1</v>
       </c>
       <c r="P15">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:16">
       <c r="A16">
-        <v>280</v>
+        <v>2860</v>
       </c>
       <c r="B16">
-        <v>0.145114</v>
+        <v>0.413493625</v>
       </c>
       <c r="C16">
-        <v>0.74</v>
+        <v>0.745</v>
       </c>
       <c r="D16">
-        <v>0.265</v>
+        <v>0.745</v>
       </c>
       <c r="E16">
-        <v>0.6320747085995552</v>
+        <v>0.808941235556802</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>0.995</v>
       </c>
       <c r="I16">
         <v>0.2</v>
       </c>
       <c r="J16">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="K16">
         <v>0.5</v>
@@ -1174,39 +1174,39 @@
         <v>1</v>
       </c>
       <c r="P16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:16">
       <c r="A17">
-        <v>300</v>
+        <v>2380</v>
       </c>
       <c r="B17">
-        <v>0.145114</v>
+        <v>0.407966625</v>
       </c>
       <c r="C17">
+        <v>0.7425</v>
+      </c>
+      <c r="D17">
         <v>0.74</v>
       </c>
-      <c r="D17">
-        <v>0.265</v>
-      </c>
       <c r="E17">
-        <v>0.6331645125661524</v>
+        <v>0.8086191379400079</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17">
-        <v>0.99</v>
+        <v>0.995</v>
       </c>
       <c r="I17">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="J17">
         <v>0.5</v>
       </c>
       <c r="K17">
-        <v>0.5</v>
+        <v>0.233333333333333</v>
       </c>
       <c r="L17">
         <v>1</v>
@@ -1221,39 +1221,39 @@
         <v>1</v>
       </c>
       <c r="P17">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:16">
       <c r="A18">
-        <v>320</v>
+        <v>2460</v>
       </c>
       <c r="B18">
-        <v>0.145114</v>
+        <v>0.407966625</v>
       </c>
       <c r="C18">
+        <v>0.7425</v>
+      </c>
+      <c r="D18">
         <v>0.74</v>
       </c>
-      <c r="D18">
-        <v>0.265</v>
-      </c>
       <c r="E18">
-        <v>0.6335822707533481</v>
+        <v>0.808500470396978</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18">
-        <v>0.985</v>
+        <v>0.995</v>
       </c>
       <c r="I18">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="J18">
         <v>0.5</v>
       </c>
       <c r="K18">
-        <v>0.5</v>
+        <v>0.266666666666667</v>
       </c>
       <c r="L18">
         <v>1</v>
@@ -1268,39 +1268,39 @@
         <v>1</v>
       </c>
       <c r="P18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:16">
       <c r="A19">
-        <v>340</v>
+        <v>2960</v>
       </c>
       <c r="B19">
-        <v>0.145114</v>
+        <v>0.413493625</v>
       </c>
       <c r="C19">
-        <v>0.74</v>
+        <v>0.745</v>
       </c>
       <c r="D19">
-        <v>0.265</v>
+        <v>0.745</v>
       </c>
       <c r="E19">
-        <v>0.6339273753427704</v>
+        <v>0.808334578015396</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="I19">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="J19">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K19">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L19">
         <v>1</v>
@@ -1315,39 +1315,39 @@
         <v>1</v>
       </c>
       <c r="P19">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:16">
       <c r="A20">
-        <v>360</v>
+        <v>2300</v>
       </c>
       <c r="B20">
-        <v>0.145114</v>
+        <v>0.407966625</v>
       </c>
       <c r="C20">
+        <v>0.7425</v>
+      </c>
+      <c r="D20">
         <v>0.74</v>
       </c>
-      <c r="D20">
-        <v>0.265</v>
-      </c>
       <c r="E20">
-        <v>0.6332553295633688</v>
+        <v>0.808228019405329</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20">
-        <v>0.995</v>
+        <v>0.98</v>
       </c>
       <c r="I20">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J20">
         <v>0.5</v>
       </c>
       <c r="K20">
-        <v>0.5</v>
+        <v>0.266666666666667</v>
       </c>
       <c r="L20">
         <v>1</v>
@@ -1362,39 +1362,39 @@
         <v>1</v>
       </c>
       <c r="P20">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:16">
       <c r="A21">
-        <v>380</v>
+        <v>2280</v>
       </c>
       <c r="B21">
-        <v>0.145114</v>
+        <v>0.407966625</v>
       </c>
       <c r="C21">
+        <v>0.7425</v>
+      </c>
+      <c r="D21">
         <v>0.74</v>
       </c>
-      <c r="D21">
-        <v>0.265</v>
-      </c>
       <c r="E21">
-        <v>0.6326559373817404</v>
+        <v>0.807928928761163</v>
       </c>
       <c r="G21">
         <v>1</v>
       </c>
       <c r="H21">
-        <v>0.99</v>
+        <v>0.985</v>
       </c>
       <c r="I21">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="J21">
         <v>0.5</v>
       </c>
       <c r="K21">
-        <v>0.5</v>
+        <v>0.233333333333333</v>
       </c>
       <c r="L21">
         <v>1</v>
@@ -1409,24 +1409,24 @@
         <v>1</v>
       </c>
       <c r="P21">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:16">
       <c r="A22">
-        <v>400</v>
+        <v>2340</v>
       </c>
       <c r="B22">
-        <v>0.145114</v>
+        <v>0.407966625</v>
       </c>
       <c r="C22">
+        <v>0.7425</v>
+      </c>
+      <c r="D22">
         <v>0.74</v>
       </c>
-      <c r="D22">
-        <v>0.265</v>
-      </c>
       <c r="E22">
-        <v>0.6324924667867508</v>
+        <v>0.807720655114213</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1435,13 +1435,13 @@
         <v>0.995</v>
       </c>
       <c r="I22">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="J22">
         <v>0.5</v>
       </c>
       <c r="K22">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="L22">
         <v>1</v>
@@ -1456,24 +1456,24 @@
         <v>1</v>
       </c>
       <c r="P22">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:16">
       <c r="A23">
-        <v>420</v>
+        <v>2440</v>
       </c>
       <c r="B23">
-        <v>0.145114</v>
+        <v>0.407966625</v>
       </c>
       <c r="C23">
+        <v>0.7425</v>
+      </c>
+      <c r="D23">
         <v>0.74</v>
       </c>
-      <c r="D23">
-        <v>0.265</v>
-      </c>
       <c r="E23">
-        <v>0.6326559373817404</v>
+        <v>0.807646790623144</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1482,13 +1482,13 @@
         <v>0.99</v>
       </c>
       <c r="I23">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="J23">
         <v>0.5</v>
       </c>
       <c r="K23">
-        <v>0.5</v>
+        <v>0.266666666666667</v>
       </c>
       <c r="L23">
         <v>1</v>
@@ -1503,40 +1503,40 @@
         <v>1</v>
       </c>
       <c r="P23">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:16">
       <c r="A24">
-        <v>440</v>
+        <v>2540</v>
       </c>
       <c r="B24">
-        <v>0.145114</v>
+        <v>0.413493625</v>
       </c>
       <c r="C24">
-        <v>0.74</v>
+        <v>0.745</v>
       </c>
       <c r="D24">
-        <v>0.265</v>
+        <v>0.745</v>
       </c>
       <c r="E24">
-        <v>0.634526767524399</v>
+        <v>0.807183018490692</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
       <c r="H24">
-        <v>0.995</v>
+        <v>0.985</v>
       </c>
       <c r="I24">
+        <v>0.25</v>
+      </c>
+      <c r="J24">
+        <v>0.4</v>
+      </c>
+      <c r="K24">
         <v>0.3</v>
       </c>
-      <c r="J24">
-        <v>0.5</v>
-      </c>
-      <c r="K24">
-        <v>0.5</v>
-      </c>
       <c r="L24">
         <v>1</v>
       </c>
@@ -1550,39 +1550,39 @@
         <v>1</v>
       </c>
       <c r="P24">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:16">
       <c r="A25">
-        <v>460</v>
+        <v>2420</v>
       </c>
       <c r="B25">
-        <v>0.145114</v>
+        <v>0.407966625</v>
       </c>
       <c r="C25">
+        <v>0.7425</v>
+      </c>
+      <c r="D25">
         <v>0.74</v>
       </c>
-      <c r="D25">
-        <v>0.265</v>
-      </c>
       <c r="E25">
-        <v>0.6323289961917612</v>
+        <v>0.806612687748172</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="I25">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="J25">
         <v>0.5</v>
       </c>
       <c r="K25">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="L25">
         <v>1</v>
@@ -1597,36 +1597,36 @@
         <v>1</v>
       </c>
       <c r="P25">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:16">
       <c r="A26">
-        <v>480</v>
+        <v>2900</v>
       </c>
       <c r="B26">
-        <v>0.145114</v>
+        <v>0.413493625</v>
       </c>
       <c r="C26">
-        <v>0.74</v>
+        <v>0.745</v>
       </c>
       <c r="D26">
-        <v>0.265</v>
+        <v>0.745</v>
       </c>
       <c r="E26">
-        <v>0.6334188001583585</v>
+        <v>0.806543666830288</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26">
-        <v>0.99</v>
+        <v>0.975</v>
       </c>
       <c r="I26">
         <v>0.26</v>
       </c>
       <c r="J26">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="K26">
         <v>0.5</v>
@@ -1644,24 +1644,24 @@
         <v>1</v>
       </c>
       <c r="P26">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:16">
       <c r="A27">
-        <v>500</v>
+        <v>2160</v>
       </c>
       <c r="B27">
-        <v>0.145114</v>
+        <v>0.407966625</v>
       </c>
       <c r="C27">
+        <v>0.7425</v>
+      </c>
+      <c r="D27">
         <v>0.74</v>
       </c>
-      <c r="D27">
-        <v>0.265</v>
-      </c>
       <c r="E27">
-        <v>0.6315661334151431</v>
+        <v>0.804760021004957</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1670,13 +1670,13 @@
         <v>1</v>
       </c>
       <c r="I27">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="J27">
         <v>0.5</v>
       </c>
       <c r="K27">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="L27">
         <v>1</v>
@@ -1691,39 +1691,39 @@
         <v>1</v>
       </c>
       <c r="P27">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:16">
       <c r="A28">
-        <v>520</v>
+        <v>2260</v>
       </c>
       <c r="B28">
-        <v>0.145114</v>
+        <v>0.407966625</v>
       </c>
       <c r="C28">
+        <v>0.7425</v>
+      </c>
+      <c r="D28">
         <v>0.74</v>
       </c>
-      <c r="D28">
-        <v>0.265</v>
-      </c>
       <c r="E28">
-        <v>0.6331645125661524</v>
+        <v>0.804560223611081</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28">
-        <v>0.99</v>
+        <v>0.975</v>
       </c>
       <c r="I28">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="J28">
         <v>0.5</v>
       </c>
       <c r="K28">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="L28">
         <v>1</v>
@@ -1738,24 +1738,24 @@
         <v>1</v>
       </c>
       <c r="P28">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:16">
       <c r="A29">
-        <v>540</v>
+        <v>2320</v>
       </c>
       <c r="B29">
-        <v>0.145114</v>
+        <v>0.407966625</v>
       </c>
       <c r="C29">
+        <v>0.7425</v>
+      </c>
+      <c r="D29">
         <v>0.74</v>
       </c>
-      <c r="D29">
-        <v>0.265</v>
-      </c>
       <c r="E29">
-        <v>0.6327467543789567</v>
+        <v>0.804279296366358</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1764,13 +1764,13 @@
         <v>0.995</v>
       </c>
       <c r="I29">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="J29">
         <v>0.5</v>
       </c>
       <c r="K29">
-        <v>0.5</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="L29">
         <v>1</v>
@@ -1785,39 +1785,39 @@
         <v>1</v>
       </c>
       <c r="P29">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:16">
       <c r="A30">
-        <v>560</v>
+        <v>2360</v>
       </c>
       <c r="B30">
-        <v>0.145114</v>
+        <v>0.407966625</v>
       </c>
       <c r="C30">
+        <v>0.7425</v>
+      </c>
+      <c r="D30">
         <v>0.74</v>
       </c>
-      <c r="D30">
-        <v>0.265</v>
-      </c>
       <c r="E30">
-        <v>0.6315479700156998</v>
+        <v>0.804188479369142</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30">
-        <v>0.985</v>
+        <v>0.99</v>
       </c>
       <c r="I30">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="J30">
         <v>0.5</v>
       </c>
       <c r="K30">
-        <v>0.5</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="L30">
         <v>1</v>
@@ -1832,39 +1832,39 @@
         <v>1</v>
       </c>
       <c r="P30">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:16">
       <c r="A31">
-        <v>580</v>
+        <v>2660</v>
       </c>
       <c r="B31">
-        <v>0.1443065</v>
+        <v>0.413493625</v>
       </c>
       <c r="C31">
         <v>0.745</v>
       </c>
       <c r="D31">
-        <v>0.26</v>
+        <v>0.745</v>
       </c>
       <c r="E31">
-        <v>0.6333279831611419</v>
+        <v>0.803685958651211</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31">
-        <v>0.985</v>
+        <v>0.995</v>
       </c>
       <c r="I31">
-        <v>0.26</v>
+        <v>0.18</v>
       </c>
       <c r="J31">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K31">
-        <v>0.5</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="L31">
         <v>1</v>
@@ -1879,39 +1879,39 @@
         <v>1</v>
       </c>
       <c r="P31">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:16">
       <c r="A32">
-        <v>600</v>
+        <v>2620</v>
       </c>
       <c r="B32">
-        <v>0.1443065</v>
+        <v>0.413493625</v>
       </c>
       <c r="C32">
         <v>0.745</v>
       </c>
       <c r="D32">
-        <v>0.26</v>
+        <v>0.745</v>
       </c>
       <c r="E32">
-        <v>0.6347810551166049</v>
+        <v>0.803578189147847</v>
       </c>
       <c r="G32">
         <v>1</v>
       </c>
       <c r="H32">
-        <v>0.995</v>
+        <v>0.99</v>
       </c>
       <c r="I32">
         <v>0.31</v>
       </c>
       <c r="J32">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K32">
-        <v>0.5</v>
+        <v>0.266666666666667</v>
       </c>
       <c r="L32">
         <v>1</v>
@@ -1926,42 +1926,42 @@
         <v>1</v>
       </c>
       <c r="P32">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33">
-        <v>620</v>
+        <v>2220</v>
       </c>
       <c r="B33">
-        <v>0.480261375</v>
+        <v>0.407966625</v>
       </c>
       <c r="C33">
-        <v>0.985</v>
+        <v>0.7425</v>
       </c>
       <c r="D33">
-        <v>0.495</v>
+        <v>0.74</v>
       </c>
       <c r="E33">
-        <v>0.7864222529270147</v>
+        <v>0.80351643358974</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33">
-        <v>0.99</v>
+        <v>0.995</v>
       </c>
       <c r="I33">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="J33">
         <v>0.5</v>
       </c>
       <c r="K33">
-        <v>0.5</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="L33">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M33">
         <v>0.5</v>
@@ -1978,37 +1978,37 @@
     </row>
     <row r="34" spans="1:16">
       <c r="A34">
-        <v>640</v>
+        <v>2640</v>
       </c>
       <c r="B34">
-        <v>0.480261375</v>
+        <v>0.413493625</v>
       </c>
       <c r="C34">
+        <v>0.745</v>
+      </c>
+      <c r="D34">
+        <v>0.745</v>
+      </c>
+      <c r="E34">
+        <v>0.803131369521543</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
         <v>0.985</v>
       </c>
-      <c r="D34">
-        <v>0.495</v>
-      </c>
-      <c r="E34">
-        <v>0.7870216451086433</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-      <c r="H34">
-        <v>0.995</v>
-      </c>
       <c r="I34">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="J34">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="K34">
-        <v>0.5</v>
+        <v>0.366666666666667</v>
       </c>
       <c r="L34">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M34">
         <v>0.5</v>
@@ -2025,19 +2025,19 @@
     </row>
     <row r="35" spans="1:16">
       <c r="A35">
-        <v>660</v>
+        <v>3020</v>
       </c>
       <c r="B35">
-        <v>0.003825375</v>
+        <v>0.413493625</v>
       </c>
       <c r="C35">
-        <v>0.505</v>
+        <v>0.745</v>
       </c>
       <c r="D35">
-        <v>0.015</v>
+        <v>0.745</v>
       </c>
       <c r="E35">
-        <v>0.605902935565247</v>
+        <v>0.802584045751651</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2046,10 +2046,10 @@
         <v>0.995</v>
       </c>
       <c r="I35">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="J35">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K35">
         <v>0.5</v>
@@ -2061,45 +2061,45 @@
         <v>0.5</v>
       </c>
       <c r="N35">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O35">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P35">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36">
-        <v>680</v>
+        <v>2680</v>
       </c>
       <c r="B36">
-        <v>0.003825375</v>
+        <v>0.413493625</v>
       </c>
       <c r="C36">
-        <v>0.505</v>
+        <v>0.745</v>
       </c>
       <c r="D36">
-        <v>0.015</v>
+        <v>0.745</v>
       </c>
       <c r="E36">
-        <v>0.6057213015708141</v>
+        <v>0.802442371235994</v>
       </c>
       <c r="G36">
         <v>1</v>
       </c>
       <c r="H36">
-        <v>0.985</v>
+        <v>0.99</v>
       </c>
       <c r="I36">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J36">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K36">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L36">
         <v>1</v>
@@ -2108,30 +2108,30 @@
         <v>0.5</v>
       </c>
       <c r="N36">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O36">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P36">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:16">
       <c r="A37">
-        <v>700</v>
+        <v>2600</v>
       </c>
       <c r="B37">
-        <v>0.003825375</v>
+        <v>0.413493625</v>
       </c>
       <c r="C37">
-        <v>0.505</v>
+        <v>0.745</v>
       </c>
       <c r="D37">
-        <v>0.015</v>
+        <v>0.745</v>
       </c>
       <c r="E37">
-        <v>0.6053035433836186</v>
+        <v>0.801408268361023</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2140,13 +2140,13 @@
         <v>0.99</v>
       </c>
       <c r="I37">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="J37">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K37">
-        <v>0.5</v>
+        <v>0.233333333333333</v>
       </c>
       <c r="L37">
         <v>1</v>
@@ -2155,45 +2155,45 @@
         <v>0.5</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O37">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P37">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:16">
       <c r="A38">
-        <v>720</v>
+        <v>2700</v>
       </c>
       <c r="B38">
-        <v>0.003825375</v>
+        <v>0.413493625</v>
       </c>
       <c r="C38">
-        <v>0.505</v>
+        <v>0.745</v>
       </c>
       <c r="D38">
-        <v>0.015</v>
+        <v>0.745</v>
       </c>
       <c r="E38">
-        <v>0.6062298767552261</v>
+        <v>0.800972346774384</v>
       </c>
       <c r="G38">
         <v>1</v>
       </c>
       <c r="H38">
-        <v>0.985</v>
+        <v>0.98</v>
       </c>
       <c r="I38">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="J38">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K38">
-        <v>0.5</v>
+        <v>0.233333333333333</v>
       </c>
       <c r="L38">
         <v>1</v>
@@ -2202,45 +2202,45 @@
         <v>0.5</v>
       </c>
       <c r="N38">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O38">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P38">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:16">
       <c r="A39">
-        <v>740</v>
+        <v>2560</v>
       </c>
       <c r="B39">
-        <v>0.003825375</v>
+        <v>0.413493625</v>
       </c>
       <c r="C39">
-        <v>0.505</v>
+        <v>0.745</v>
       </c>
       <c r="D39">
-        <v>0.015</v>
+        <v>0.745</v>
       </c>
       <c r="E39">
-        <v>0.605902935565247</v>
+        <v>0.8002724504491689</v>
       </c>
       <c r="G39">
         <v>1</v>
       </c>
       <c r="H39">
-        <v>0.995</v>
+        <v>0.99</v>
       </c>
       <c r="I39">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="J39">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K39">
-        <v>0.5</v>
+        <v>0.266666666666667</v>
       </c>
       <c r="L39">
         <v>1</v>
@@ -2249,45 +2249,45 @@
         <v>0.5</v>
       </c>
       <c r="N39">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O39">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P39">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:16">
       <c r="A40">
-        <v>760</v>
+        <v>2980</v>
       </c>
       <c r="B40">
-        <v>0.0051005</v>
+        <v>0.413493625</v>
       </c>
       <c r="C40">
-        <v>0.505</v>
+        <v>0.745</v>
       </c>
       <c r="D40">
-        <v>0.02</v>
+        <v>0.745</v>
       </c>
       <c r="E40">
-        <v>0.6060664061602365</v>
+        <v>0.800266395982688</v>
       </c>
       <c r="G40">
         <v>1</v>
       </c>
       <c r="H40">
-        <v>0.99</v>
+        <v>0.985</v>
       </c>
       <c r="I40">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="J40">
         <v>0.5</v>
       </c>
       <c r="K40">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="L40">
         <v>1</v>
@@ -2296,30 +2296,30 @@
         <v>0.5</v>
       </c>
       <c r="N40">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O40">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P40">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:16">
       <c r="A41">
-        <v>780</v>
+        <v>2740</v>
       </c>
       <c r="B41">
-        <v>0.0051005</v>
+        <v>0.413493625</v>
       </c>
       <c r="C41">
-        <v>0.505</v>
+        <v>0.745</v>
       </c>
       <c r="D41">
-        <v>0.02</v>
+        <v>0.745</v>
       </c>
       <c r="E41">
-        <v>0.6063206937524426</v>
+        <v>0.80015378290614</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -2328,13 +2328,13 @@
         <v>0.99</v>
       </c>
       <c r="I41">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="J41">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="K41">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L41">
         <v>1</v>
@@ -2343,45 +2343,45 @@
         <v>0.5</v>
       </c>
       <c r="N41">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O41">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P41">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:16">
       <c r="A42">
-        <v>800</v>
+        <v>3000</v>
       </c>
       <c r="B42">
-        <v>0.003825375</v>
+        <v>0.413493625</v>
       </c>
       <c r="C42">
-        <v>0.505</v>
+        <v>0.745</v>
       </c>
       <c r="D42">
-        <v>0.015</v>
+        <v>0.745</v>
       </c>
       <c r="E42">
-        <v>0.6065749813446487</v>
+        <v>0.799073666085912</v>
       </c>
       <c r="G42">
         <v>1</v>
       </c>
       <c r="H42">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="I42">
         <v>0.28</v>
       </c>
       <c r="J42">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="K42">
-        <v>0.5</v>
+        <v>0.266666666666667</v>
       </c>
       <c r="L42">
         <v>1</v>
@@ -2390,45 +2390,45 @@
         <v>0.5</v>
       </c>
       <c r="N42">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O42">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P42">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:16">
       <c r="A43">
-        <v>820</v>
+        <v>2580</v>
       </c>
       <c r="B43">
-        <v>0.003825375</v>
+        <v>0.413493625</v>
       </c>
       <c r="C43">
-        <v>0.505</v>
+        <v>0.745</v>
       </c>
       <c r="D43">
-        <v>0.015</v>
+        <v>0.745</v>
       </c>
       <c r="E43">
-        <v>0.604958438794196</v>
+        <v>0.798447634251767</v>
       </c>
       <c r="G43">
         <v>1</v>
       </c>
       <c r="H43">
-        <v>0.985</v>
+        <v>0.995</v>
       </c>
       <c r="I43">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="J43">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="K43">
-        <v>0.5</v>
+        <v>0.233333333333333</v>
       </c>
       <c r="L43">
         <v>1</v>
@@ -2437,30 +2437,30 @@
         <v>0.5</v>
       </c>
       <c r="N43">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O43">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P43">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:16">
       <c r="A44">
-        <v>840</v>
+        <v>2480</v>
       </c>
       <c r="B44">
-        <v>0.003825375</v>
+        <v>0.4107185</v>
       </c>
       <c r="C44">
-        <v>0.505</v>
+        <v>0.745</v>
       </c>
       <c r="D44">
-        <v>0.015</v>
+        <v>0.74</v>
       </c>
       <c r="E44">
-        <v>0.6060664061602365</v>
+        <v>0.797475286934903</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -2469,13 +2469,13 @@
         <v>0.99</v>
       </c>
       <c r="I44">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="J44">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="K44">
-        <v>0.5</v>
+        <v>0.266666666666667</v>
       </c>
       <c r="L44">
         <v>1</v>
@@ -2484,45 +2484,45 @@
         <v>0.5</v>
       </c>
       <c r="N44">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O44">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P44">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:16">
       <c r="A45">
-        <v>860</v>
+        <v>2720</v>
       </c>
       <c r="B45">
-        <v>0.003825375</v>
+        <v>0.413493625</v>
       </c>
       <c r="C45">
-        <v>0.505</v>
+        <v>0.745</v>
       </c>
       <c r="D45">
-        <v>0.015</v>
+        <v>0.745</v>
       </c>
       <c r="E45">
-        <v>0.6066657983418651</v>
+        <v>0.7968867927929399</v>
       </c>
       <c r="G45">
         <v>1</v>
       </c>
       <c r="H45">
-        <v>0.995</v>
+        <v>0.98</v>
       </c>
       <c r="I45">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="J45">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K45">
-        <v>0.5</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="L45">
         <v>1</v>
@@ -2531,45 +2531,45 @@
         <v>0.5</v>
       </c>
       <c r="N45">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O45">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P45">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:16">
       <c r="A46">
-        <v>880</v>
+        <v>2500</v>
       </c>
       <c r="B46">
-        <v>0.003825375</v>
+        <v>0.413493625</v>
       </c>
       <c r="C46">
-        <v>0.505</v>
+        <v>0.745</v>
       </c>
       <c r="D46">
-        <v>0.015</v>
+        <v>0.745</v>
       </c>
       <c r="E46">
-        <v>0.6053035433836186</v>
+        <v>0.794842804908923</v>
       </c>
       <c r="G46">
         <v>1</v>
       </c>
       <c r="H46">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="I46">
         <v>0.23</v>
       </c>
       <c r="J46">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="K46">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="L46">
         <v>1</v>
@@ -2578,45 +2578,45 @@
         <v>0.5</v>
       </c>
       <c r="N46">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O46">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P46">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:16">
       <c r="A47">
-        <v>900</v>
+        <v>2520</v>
       </c>
       <c r="B47">
-        <v>0.003825375</v>
+        <v>0.413493625</v>
       </c>
       <c r="C47">
-        <v>0.505</v>
+        <v>0.745</v>
       </c>
       <c r="D47">
-        <v>0.015</v>
+        <v>0.745</v>
       </c>
       <c r="E47">
-        <v>0.6053943603808349</v>
+        <v>0.791219812166635</v>
       </c>
       <c r="G47">
         <v>1</v>
       </c>
       <c r="H47">
-        <v>0.995</v>
+        <v>0.99</v>
       </c>
       <c r="I47">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="J47">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="K47">
-        <v>0.5</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="L47">
         <v>1</v>
@@ -2625,30 +2625,30 @@
         <v>0.5</v>
       </c>
       <c r="N47">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O47">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P47">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:16">
       <c r="A48">
-        <v>920</v>
+        <v>640</v>
       </c>
       <c r="B48">
-        <v>0.003825375</v>
+        <v>0.480261375</v>
       </c>
       <c r="C48">
-        <v>0.505</v>
+        <v>0.985</v>
       </c>
       <c r="D48">
-        <v>0.015</v>
+        <v>0.495</v>
       </c>
       <c r="E48">
-        <v>0.605648647973041</v>
+        <v>0.787021645108643</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -2657,7 +2657,7 @@
         <v>0.995</v>
       </c>
       <c r="I48">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="J48">
         <v>0.5</v>
@@ -2666,45 +2666,45 @@
         <v>0.5</v>
       </c>
       <c r="L48">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M48">
         <v>0.5</v>
       </c>
       <c r="N48">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O48">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P48">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:16">
       <c r="A49">
-        <v>940</v>
+        <v>620</v>
       </c>
       <c r="B49">
-        <v>0.0051005</v>
+        <v>0.480261375</v>
       </c>
       <c r="C49">
-        <v>0.505</v>
+        <v>0.985</v>
       </c>
       <c r="D49">
-        <v>0.02</v>
+        <v>0.495</v>
       </c>
       <c r="E49">
-        <v>0.6043590466125676</v>
+        <v>0.786422252927015</v>
       </c>
       <c r="G49">
         <v>1</v>
       </c>
       <c r="H49">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="I49">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="J49">
         <v>0.5</v>
@@ -2713,48 +2713,48 @@
         <v>0.5</v>
       </c>
       <c r="L49">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M49">
         <v>0.5</v>
       </c>
       <c r="N49">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O49">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P49">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:16">
       <c r="A50">
-        <v>960</v>
+        <v>1</v>
       </c>
       <c r="B50">
-        <v>0.0051005</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>0.505</v>
+        <v>0.5</v>
       </c>
       <c r="D50">
-        <v>0.02</v>
+        <v>0.26</v>
       </c>
       <c r="E50">
-        <v>0.6067566153390815</v>
+        <v>0.651400565607213</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
       <c r="I50">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="J50">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K50">
         <v>0.5</v>
@@ -2766,10 +2766,10 @@
         <v>0.5</v>
       </c>
       <c r="N50">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O50">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P50">
         <v>0.5</v>
@@ -2777,31 +2777,31 @@
     </row>
     <row r="51" spans="1:16">
       <c r="A51">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="B51">
-        <v>0.0051005</v>
+        <v>0.065</v>
       </c>
       <c r="C51">
-        <v>0.505</v>
+        <v>0.5</v>
       </c>
       <c r="D51">
-        <v>0.02</v>
+        <v>0.26</v>
       </c>
       <c r="E51">
-        <v>0.6038686348275989</v>
+        <v>0.650964644020574</v>
       </c>
       <c r="G51">
         <v>1</v>
       </c>
       <c r="H51">
-        <v>0.995</v>
+        <v>0.99</v>
       </c>
       <c r="I51">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="J51">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K51">
         <v>0.5</v>
@@ -2813,10 +2813,10 @@
         <v>0.5</v>
       </c>
       <c r="N51">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O51">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P51">
         <v>0.5</v>
@@ -2824,31 +2824,31 @@
     </row>
     <row r="52" spans="1:16">
       <c r="A52">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="B52">
-        <v>0.0051005</v>
+        <v>0.065</v>
       </c>
       <c r="C52">
-        <v>0.505</v>
+        <v>0.5</v>
       </c>
       <c r="D52">
-        <v>0.02</v>
+        <v>0.26</v>
       </c>
       <c r="E52">
-        <v>0.6059755891630202</v>
+        <v>0.650801173425584</v>
       </c>
       <c r="G52">
         <v>1</v>
       </c>
       <c r="H52">
-        <v>0.985</v>
+        <v>0.995</v>
       </c>
       <c r="I52">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="J52">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K52">
         <v>0.5</v>
@@ -2860,10 +2860,10 @@
         <v>0.5</v>
       </c>
       <c r="N52">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O52">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P52">
         <v>0.5</v>
@@ -2871,31 +2871,31 @@
     </row>
     <row r="53" spans="1:16">
       <c r="A53">
-        <v>1020</v>
+        <v>80</v>
       </c>
       <c r="B53">
-        <v>0.0051005</v>
+        <v>0.065</v>
       </c>
       <c r="C53">
-        <v>0.505</v>
+        <v>0.5</v>
       </c>
       <c r="D53">
-        <v>0.02</v>
+        <v>0.26</v>
       </c>
       <c r="E53">
-        <v>0.6050492557914126</v>
+        <v>0.650619539431151</v>
       </c>
       <c r="G53">
         <v>1</v>
       </c>
       <c r="H53">
-        <v>0.99</v>
+        <v>0.985</v>
       </c>
       <c r="I53">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="J53">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K53">
         <v>0.5</v>
@@ -2907,10 +2907,10 @@
         <v>0.5</v>
       </c>
       <c r="N53">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O53">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P53">
         <v>0.5</v>
@@ -2918,31 +2918,31 @@
     </row>
     <row r="54" spans="1:16">
       <c r="A54">
-        <v>1040</v>
+        <v>20</v>
       </c>
       <c r="B54">
-        <v>0.0051005</v>
+        <v>0.065</v>
       </c>
       <c r="C54">
-        <v>0.505</v>
+        <v>0.5</v>
       </c>
       <c r="D54">
-        <v>0.02</v>
+        <v>0.26</v>
       </c>
       <c r="E54">
-        <v>0.6058121185680306</v>
+        <v>0.650129127646182</v>
       </c>
       <c r="G54">
         <v>1</v>
       </c>
       <c r="H54">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="I54">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="J54">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K54">
         <v>0.5</v>
@@ -2954,10 +2954,10 @@
         <v>0.5</v>
       </c>
       <c r="N54">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O54">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P54">
         <v>0.5</v>
@@ -2965,28 +2965,28 @@
     </row>
     <row r="55" spans="1:16">
       <c r="A55">
-        <v>1060</v>
+        <v>1160</v>
       </c>
       <c r="B55">
-        <v>0.0051005</v>
+        <v>0.4107185</v>
       </c>
       <c r="C55">
-        <v>0.505</v>
+        <v>0.745</v>
       </c>
       <c r="D55">
-        <v>0.02</v>
+        <v>0.74</v>
       </c>
       <c r="E55">
-        <v>0.604958438794196</v>
+        <v>0.63552575449378</v>
       </c>
       <c r="G55">
         <v>1</v>
       </c>
       <c r="H55">
-        <v>0.985</v>
+        <v>0.98</v>
       </c>
       <c r="I55">
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="J55">
         <v>0.5</v>
@@ -3001,10 +3001,10 @@
         <v>0.5</v>
       </c>
       <c r="N55">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O55">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P55">
         <v>0.5</v>
@@ -3012,28 +3012,28 @@
     </row>
     <row r="56" spans="1:16">
       <c r="A56">
-        <v>1080</v>
+        <v>1700</v>
       </c>
       <c r="B56">
-        <v>0.0051005</v>
+        <v>0.4107185</v>
       </c>
       <c r="C56">
-        <v>0.505</v>
+        <v>0.745</v>
       </c>
       <c r="D56">
-        <v>0.02</v>
+        <v>0.74</v>
       </c>
       <c r="E56">
-        <v>0.6059755891630202</v>
+        <v>0.635453100896007</v>
       </c>
       <c r="G56">
         <v>1</v>
       </c>
       <c r="H56">
-        <v>0.985</v>
+        <v>0.99</v>
       </c>
       <c r="I56">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="J56">
         <v>0.5</v>
@@ -3048,10 +3048,10 @@
         <v>0.5</v>
       </c>
       <c r="N56">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O56">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P56">
         <v>0.5</v>
@@ -3059,34 +3059,34 @@
     </row>
     <row r="57" spans="1:16">
       <c r="A57">
-        <v>1100</v>
+        <v>1840</v>
       </c>
       <c r="B57">
-        <v>0.1443065</v>
+        <v>0.4107185</v>
       </c>
       <c r="C57">
         <v>0.745</v>
       </c>
       <c r="D57">
-        <v>0.26</v>
+        <v>0.74</v>
       </c>
       <c r="E57">
-        <v>0.6209538645670787</v>
+        <v>0.635035342708811</v>
       </c>
       <c r="G57">
         <v>1</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>0.995</v>
       </c>
       <c r="I57">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="J57">
         <v>0.5</v>
       </c>
       <c r="K57">
-        <v>0.2666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="L57">
         <v>1</v>
@@ -3106,34 +3106,34 @@
     </row>
     <row r="58" spans="1:16">
       <c r="A58">
-        <v>1120</v>
+        <v>1760</v>
       </c>
       <c r="B58">
-        <v>0.1443065</v>
+        <v>0.4107185</v>
       </c>
       <c r="C58">
         <v>0.745</v>
       </c>
       <c r="D58">
-        <v>0.26</v>
+        <v>0.74</v>
       </c>
       <c r="E58">
-        <v>0.618811794326067</v>
+        <v>0.635017179309368</v>
       </c>
       <c r="G58">
         <v>1</v>
       </c>
       <c r="H58">
-        <v>0.995</v>
+        <v>0.98</v>
       </c>
       <c r="I58">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="J58">
         <v>0.5</v>
       </c>
       <c r="K58">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="L58">
         <v>1</v>
@@ -3153,7 +3153,7 @@
     </row>
     <row r="59" spans="1:16">
       <c r="A59">
-        <v>1140</v>
+        <v>600</v>
       </c>
       <c r="B59">
         <v>0.1443065</v>
@@ -3165,16 +3165,16 @@
         <v>0.26</v>
       </c>
       <c r="E59">
-        <v>0.6321473621973284</v>
+        <v>0.634781055116605</v>
       </c>
       <c r="G59">
         <v>1</v>
       </c>
       <c r="H59">
-        <v>0.99</v>
+        <v>0.995</v>
       </c>
       <c r="I59">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="J59">
         <v>0.5</v>
@@ -3200,28 +3200,28 @@
     </row>
     <row r="60" spans="1:16">
       <c r="A60">
-        <v>1160</v>
+        <v>440</v>
       </c>
       <c r="B60">
-        <v>0.4107185</v>
+        <v>0.145114</v>
       </c>
       <c r="C60">
-        <v>0.745</v>
+        <v>0.74</v>
       </c>
       <c r="D60">
-        <v>0.74</v>
+        <v>0.265</v>
       </c>
       <c r="E60">
-        <v>0.6355257544937797</v>
+        <v>0.634526767524399</v>
       </c>
       <c r="G60">
         <v>1</v>
       </c>
       <c r="H60">
-        <v>0.98</v>
+        <v>0.995</v>
       </c>
       <c r="I60">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="J60">
         <v>0.5</v>
@@ -3247,28 +3247,28 @@
     </row>
     <row r="61" spans="1:16">
       <c r="A61">
-        <v>1180</v>
+        <v>180</v>
       </c>
       <c r="B61">
-        <v>0.4107185</v>
+        <v>0.06625</v>
       </c>
       <c r="C61">
-        <v>0.745</v>
+        <v>0.5</v>
       </c>
       <c r="D61">
-        <v>0.74</v>
+        <v>0.265</v>
       </c>
       <c r="E61">
-        <v>0.6311302118285042</v>
+        <v>0.634272479932193</v>
       </c>
       <c r="G61">
         <v>1</v>
       </c>
       <c r="H61">
-        <v>0.99</v>
+        <v>0.995</v>
       </c>
       <c r="I61">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="J61">
         <v>0.5</v>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="62" spans="1:16">
       <c r="A62">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="B62">
         <v>0.4107185</v>
@@ -3306,16 +3306,16 @@
         <v>0.74</v>
       </c>
       <c r="E62">
-        <v>0.6314753164179266</v>
+        <v>0.634109009337203</v>
       </c>
       <c r="G62">
         <v>1</v>
       </c>
       <c r="H62">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="I62">
-        <v>0.18</v>
+        <v>0.28</v>
       </c>
       <c r="J62">
         <v>0.5</v>
@@ -3341,7 +3341,7 @@
     </row>
     <row r="63" spans="1:16">
       <c r="A63">
-        <v>1220</v>
+        <v>1580</v>
       </c>
       <c r="B63">
         <v>0.4107185</v>
@@ -3353,16 +3353,16 @@
         <v>0.74</v>
       </c>
       <c r="E63">
-        <v>0.6318930746051223</v>
+        <v>0.634018192339987</v>
       </c>
       <c r="G63">
         <v>1</v>
       </c>
       <c r="H63">
-        <v>0.99</v>
+        <v>0.995</v>
       </c>
       <c r="I63">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="J63">
         <v>0.5</v>
@@ -3388,28 +3388,28 @@
     </row>
     <row r="64" spans="1:16">
       <c r="A64">
-        <v>1240</v>
+        <v>1420</v>
       </c>
       <c r="B64">
-        <v>0.4107185</v>
+        <v>0.1443065</v>
       </c>
       <c r="C64">
         <v>0.745</v>
       </c>
       <c r="D64">
-        <v>0.74</v>
+        <v>0.26</v>
       </c>
       <c r="E64">
-        <v>0.6324016497895343</v>
+        <v>0.634000028940544</v>
       </c>
       <c r="G64">
         <v>1</v>
       </c>
       <c r="H64">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="I64">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="J64">
         <v>0.5</v>
@@ -3435,19 +3435,19 @@
     </row>
     <row r="65" spans="1:16">
       <c r="A65">
-        <v>1260</v>
+        <v>340</v>
       </c>
       <c r="B65">
-        <v>0.4107185</v>
+        <v>0.145114</v>
       </c>
       <c r="C65">
-        <v>0.745</v>
+        <v>0.74</v>
       </c>
       <c r="D65">
-        <v>0.74</v>
+        <v>0.265</v>
       </c>
       <c r="E65">
-        <v>0.6336730877505644</v>
+        <v>0.63392737534277</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -3456,7 +3456,7 @@
         <v>0.99</v>
       </c>
       <c r="I65">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="J65">
         <v>0.5</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="66" spans="1:16">
       <c r="A66">
-        <v>1280</v>
+        <v>1520</v>
       </c>
       <c r="B66">
         <v>0.4107185</v>
@@ -3494,16 +3494,16 @@
         <v>0.74</v>
       </c>
       <c r="E66">
-        <v>0.6330010419711628</v>
+        <v>0.633836558345554</v>
       </c>
       <c r="G66">
         <v>1</v>
       </c>
       <c r="H66">
-        <v>0.995</v>
+        <v>0.985</v>
       </c>
       <c r="I66">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="J66">
         <v>0.5</v>
@@ -3529,7 +3529,7 @@
     </row>
     <row r="67" spans="1:16">
       <c r="A67">
-        <v>1300</v>
+        <v>1260</v>
       </c>
       <c r="B67">
         <v>0.4107185</v>
@@ -3541,7 +3541,7 @@
         <v>0.74</v>
       </c>
       <c r="E67">
-        <v>0.6334188001583585</v>
+        <v>0.633673087750564</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -3550,7 +3550,7 @@
         <v>0.99</v>
       </c>
       <c r="I67">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="J67">
         <v>0.5</v>
@@ -3576,19 +3576,19 @@
     </row>
     <row r="68" spans="1:16">
       <c r="A68">
-        <v>1320</v>
+        <v>1540</v>
       </c>
       <c r="B68">
-        <v>0.1443065</v>
+        <v>0.4107185</v>
       </c>
       <c r="C68">
         <v>0.745</v>
       </c>
       <c r="D68">
-        <v>0.26</v>
+        <v>0.74</v>
       </c>
       <c r="E68">
-        <v>0.6331645125661524</v>
+        <v>0.633673087750564</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -3597,7 +3597,7 @@
         <v>0.99</v>
       </c>
       <c r="I68">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="J68">
         <v>0.5</v>
@@ -3623,7 +3623,7 @@
     </row>
     <row r="69" spans="1:16">
       <c r="A69">
-        <v>1340</v>
+        <v>1480</v>
       </c>
       <c r="B69">
         <v>0.1443065</v>
@@ -3635,7 +3635,7 @@
         <v>0.26</v>
       </c>
       <c r="E69">
-        <v>0.6334188001583585</v>
+        <v>0.633673087750564</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -3644,7 +3644,7 @@
         <v>0.99</v>
       </c>
       <c r="I69">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="J69">
         <v>0.5</v>
@@ -3670,19 +3670,19 @@
     </row>
     <row r="70" spans="1:16">
       <c r="A70">
-        <v>1360</v>
+        <v>1880</v>
       </c>
       <c r="B70">
-        <v>0.1443065</v>
+        <v>0.4107185</v>
       </c>
       <c r="C70">
         <v>0.745</v>
       </c>
       <c r="D70">
-        <v>0.26</v>
+        <v>0.74</v>
       </c>
       <c r="E70">
-        <v>0.6325651203845238</v>
+        <v>0.6335822707533481</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -3691,7 +3691,7 @@
         <v>0.985</v>
       </c>
       <c r="I70">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="J70">
         <v>0.5</v>
@@ -3717,28 +3717,28 @@
     </row>
     <row r="71" spans="1:16">
       <c r="A71">
-        <v>1380</v>
+        <v>320</v>
       </c>
       <c r="B71">
-        <v>0.1443065</v>
+        <v>0.145114</v>
       </c>
       <c r="C71">
-        <v>0.745</v>
+        <v>0.74</v>
       </c>
       <c r="D71">
-        <v>0.26</v>
+        <v>0.265</v>
       </c>
       <c r="E71">
-        <v>0.6330010419711628</v>
+        <v>0.6335822707533481</v>
       </c>
       <c r="G71">
         <v>1</v>
       </c>
       <c r="H71">
-        <v>0.995</v>
+        <v>0.985</v>
       </c>
       <c r="I71">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="J71">
         <v>0.5</v>
@@ -3764,28 +3764,28 @@
     </row>
     <row r="72" spans="1:16">
       <c r="A72">
-        <v>1400</v>
+        <v>1620</v>
       </c>
       <c r="B72">
-        <v>0.1443065</v>
+        <v>0.4107185</v>
       </c>
       <c r="C72">
         <v>0.745</v>
       </c>
       <c r="D72">
+        <v>0.74</v>
+      </c>
+      <c r="E72">
+        <v>0.633509617155575</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72">
+        <v>0.995</v>
+      </c>
+      <c r="I72">
         <v>0.26</v>
-      </c>
-      <c r="E72">
-        <v>0.6319657282028954</v>
-      </c>
-      <c r="G72">
-        <v>1</v>
-      </c>
-      <c r="H72">
-        <v>0.98</v>
-      </c>
-      <c r="I72">
-        <v>0.21</v>
       </c>
       <c r="J72">
         <v>0.5</v>
@@ -3811,28 +3811,28 @@
     </row>
     <row r="73" spans="1:16">
       <c r="A73">
-        <v>1420</v>
+        <v>1300</v>
       </c>
       <c r="B73">
-        <v>0.1443065</v>
+        <v>0.4107185</v>
       </c>
       <c r="C73">
         <v>0.745</v>
       </c>
       <c r="D73">
+        <v>0.74</v>
+      </c>
+      <c r="E73">
+        <v>0.6334188001583591</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <v>0.99</v>
+      </c>
+      <c r="I73">
         <v>0.26</v>
-      </c>
-      <c r="E73">
-        <v>0.6340000289405435</v>
-      </c>
-      <c r="G73">
-        <v>1</v>
-      </c>
-      <c r="H73">
-        <v>0.98</v>
-      </c>
-      <c r="I73">
-        <v>0.29</v>
       </c>
       <c r="J73">
         <v>0.5</v>
@@ -3858,28 +3858,28 @@
     </row>
     <row r="74" spans="1:16">
       <c r="A74">
-        <v>1440</v>
+        <v>1640</v>
       </c>
       <c r="B74">
-        <v>0.1443065</v>
+        <v>0.4107185</v>
       </c>
       <c r="C74">
         <v>0.745</v>
       </c>
       <c r="D74">
+        <v>0.74</v>
+      </c>
+      <c r="E74">
+        <v>0.6334188001583591</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+      <c r="H74">
+        <v>0.99</v>
+      </c>
+      <c r="I74">
         <v>0.26</v>
-      </c>
-      <c r="E74">
-        <v>0.6330010419711628</v>
-      </c>
-      <c r="G74">
-        <v>1</v>
-      </c>
-      <c r="H74">
-        <v>0.995</v>
-      </c>
-      <c r="I74">
-        <v>0.24</v>
       </c>
       <c r="J74">
         <v>0.5</v>
@@ -3905,28 +3905,28 @@
     </row>
     <row r="75" spans="1:16">
       <c r="A75">
-        <v>1460</v>
+        <v>1660</v>
       </c>
       <c r="B75">
-        <v>0.1443065</v>
+        <v>0.4107185</v>
       </c>
       <c r="C75">
         <v>0.745</v>
       </c>
       <c r="D75">
+        <v>0.74</v>
+      </c>
+      <c r="E75">
+        <v>0.6334188001583591</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>0.99</v>
+      </c>
+      <c r="I75">
         <v>0.26</v>
-      </c>
-      <c r="E75">
-        <v>0.6322381791945447</v>
-      </c>
-      <c r="G75">
-        <v>1</v>
-      </c>
-      <c r="H75">
-        <v>0.995</v>
-      </c>
-      <c r="I75">
-        <v>0.21</v>
       </c>
       <c r="J75">
         <v>0.5</v>
@@ -3952,19 +3952,19 @@
     </row>
     <row r="76" spans="1:16">
       <c r="A76">
-        <v>1480</v>
+        <v>1680</v>
       </c>
       <c r="B76">
-        <v>0.1443065</v>
+        <v>0.4107185</v>
       </c>
       <c r="C76">
         <v>0.745</v>
       </c>
       <c r="D76">
-        <v>0.26</v>
+        <v>0.74</v>
       </c>
       <c r="E76">
-        <v>0.6336730877505644</v>
+        <v>0.6334188001583591</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -3973,7 +3973,7 @@
         <v>0.99</v>
       </c>
       <c r="I76">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="J76">
         <v>0.5</v>
@@ -3999,28 +3999,28 @@
     </row>
     <row r="77" spans="1:16">
       <c r="A77">
-        <v>1500</v>
+        <v>480</v>
       </c>
       <c r="B77">
-        <v>0.4107185</v>
+        <v>0.145114</v>
       </c>
       <c r="C77">
-        <v>0.745</v>
+        <v>0.74</v>
       </c>
       <c r="D77">
-        <v>0.74</v>
+        <v>0.265</v>
       </c>
       <c r="E77">
-        <v>0.6332553295633688</v>
+        <v>0.6334188001583591</v>
       </c>
       <c r="G77">
         <v>1</v>
       </c>
       <c r="H77">
-        <v>0.995</v>
+        <v>0.99</v>
       </c>
       <c r="I77">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="J77">
         <v>0.5</v>
@@ -4046,28 +4046,28 @@
     </row>
     <row r="78" spans="1:16">
       <c r="A78">
-        <v>1520</v>
+        <v>1340</v>
       </c>
       <c r="B78">
-        <v>0.4107185</v>
+        <v>0.1443065</v>
       </c>
       <c r="C78">
         <v>0.745</v>
       </c>
       <c r="D78">
-        <v>0.74</v>
+        <v>0.26</v>
       </c>
       <c r="E78">
-        <v>0.633836558345554</v>
+        <v>0.6334188001583591</v>
       </c>
       <c r="G78">
         <v>1</v>
       </c>
       <c r="H78">
-        <v>0.985</v>
+        <v>0.99</v>
       </c>
       <c r="I78">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="J78">
         <v>0.5</v>
@@ -4093,28 +4093,28 @@
     </row>
     <row r="79" spans="1:16">
       <c r="A79">
-        <v>1540</v>
+        <v>580</v>
       </c>
       <c r="B79">
-        <v>0.4107185</v>
+        <v>0.1443065</v>
       </c>
       <c r="C79">
         <v>0.745</v>
       </c>
       <c r="D79">
-        <v>0.74</v>
+        <v>0.26</v>
       </c>
       <c r="E79">
-        <v>0.6336730877505644</v>
+        <v>0.633327983161142</v>
       </c>
       <c r="G79">
         <v>1</v>
       </c>
       <c r="H79">
-        <v>0.99</v>
+        <v>0.985</v>
       </c>
       <c r="I79">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="J79">
         <v>0.5</v>
@@ -4140,28 +4140,28 @@
     </row>
     <row r="80" spans="1:16">
       <c r="A80">
-        <v>1560</v>
+        <v>100</v>
       </c>
       <c r="B80">
-        <v>0.4107185</v>
+        <v>0.06625</v>
       </c>
       <c r="C80">
-        <v>0.745</v>
+        <v>0.5</v>
       </c>
       <c r="D80">
-        <v>0.74</v>
+        <v>0.265</v>
       </c>
       <c r="E80">
-        <v>0.6341090093372033</v>
+        <v>0.633327983161142</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>0.985</v>
       </c>
       <c r="I80">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="J80">
         <v>0.5</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="81" spans="1:16">
       <c r="A81">
-        <v>1580</v>
+        <v>1500</v>
       </c>
       <c r="B81">
         <v>0.4107185</v>
@@ -4199,7 +4199,7 @@
         <v>0.74</v>
       </c>
       <c r="E81">
-        <v>0.6340181923399868</v>
+        <v>0.6332553295633691</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -4208,7 +4208,7 @@
         <v>0.995</v>
       </c>
       <c r="I81">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="J81">
         <v>0.5</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="82" spans="1:16">
       <c r="A82">
-        <v>1600</v>
+        <v>1860</v>
       </c>
       <c r="B82">
         <v>0.4107185</v>
@@ -4246,16 +4246,16 @@
         <v>0.74</v>
       </c>
       <c r="E82">
-        <v>0.6313118458229372</v>
+        <v>0.6332553295633691</v>
       </c>
       <c r="G82">
         <v>1</v>
       </c>
       <c r="H82">
-        <v>1</v>
+        <v>0.995</v>
       </c>
       <c r="I82">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="J82">
         <v>0.5</v>
@@ -4281,19 +4281,19 @@
     </row>
     <row r="83" spans="1:16">
       <c r="A83">
-        <v>1620</v>
+        <v>360</v>
       </c>
       <c r="B83">
-        <v>0.4107185</v>
+        <v>0.145114</v>
       </c>
       <c r="C83">
-        <v>0.745</v>
+        <v>0.74</v>
       </c>
       <c r="D83">
-        <v>0.74</v>
+        <v>0.265</v>
       </c>
       <c r="E83">
-        <v>0.6335096171555749</v>
+        <v>0.6332553295633691</v>
       </c>
       <c r="G83">
         <v>1</v>
@@ -4302,7 +4302,7 @@
         <v>0.995</v>
       </c>
       <c r="I83">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="J83">
         <v>0.5</v>
@@ -4328,19 +4328,19 @@
     </row>
     <row r="84" spans="1:16">
       <c r="A84">
-        <v>1640</v>
+        <v>300</v>
       </c>
       <c r="B84">
-        <v>0.4107185</v>
+        <v>0.145114</v>
       </c>
       <c r="C84">
-        <v>0.745</v>
+        <v>0.74</v>
       </c>
       <c r="D84">
-        <v>0.74</v>
+        <v>0.265</v>
       </c>
       <c r="E84">
-        <v>0.6334188001583585</v>
+        <v>0.633164512566152</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -4349,7 +4349,7 @@
         <v>0.99</v>
       </c>
       <c r="I84">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="J84">
         <v>0.5</v>
@@ -4375,19 +4375,19 @@
     </row>
     <row r="85" spans="1:16">
       <c r="A85">
-        <v>1660</v>
+        <v>520</v>
       </c>
       <c r="B85">
-        <v>0.4107185</v>
+        <v>0.145114</v>
       </c>
       <c r="C85">
-        <v>0.745</v>
+        <v>0.74</v>
       </c>
       <c r="D85">
-        <v>0.74</v>
+        <v>0.265</v>
       </c>
       <c r="E85">
-        <v>0.6334188001583585</v>
+        <v>0.633164512566152</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -4396,7 +4396,7 @@
         <v>0.99</v>
       </c>
       <c r="I85">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="J85">
         <v>0.5</v>
@@ -4422,19 +4422,19 @@
     </row>
     <row r="86" spans="1:16">
       <c r="A86">
-        <v>1680</v>
+        <v>1320</v>
       </c>
       <c r="B86">
-        <v>0.4107185</v>
+        <v>0.1443065</v>
       </c>
       <c r="C86">
         <v>0.745</v>
       </c>
       <c r="D86">
-        <v>0.74</v>
+        <v>0.26</v>
       </c>
       <c r="E86">
-        <v>0.6334188001583585</v>
+        <v>0.633164512566152</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -4443,7 +4443,7 @@
         <v>0.99</v>
       </c>
       <c r="I86">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="J86">
         <v>0.5</v>
@@ -4469,28 +4469,28 @@
     </row>
     <row r="87" spans="1:16">
       <c r="A87">
-        <v>1700</v>
+        <v>220</v>
       </c>
       <c r="B87">
-        <v>0.4107185</v>
+        <v>0.06625</v>
       </c>
       <c r="C87">
-        <v>0.745</v>
+        <v>0.5</v>
       </c>
       <c r="D87">
-        <v>0.74</v>
+        <v>0.265</v>
       </c>
       <c r="E87">
-        <v>0.6354531008960065</v>
+        <v>0.633073695568936</v>
       </c>
       <c r="G87">
         <v>1</v>
       </c>
       <c r="H87">
-        <v>0.99</v>
+        <v>0.985</v>
       </c>
       <c r="I87">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
       <c r="J87">
         <v>0.5</v>
@@ -4516,7 +4516,7 @@
     </row>
     <row r="88" spans="1:16">
       <c r="A88">
-        <v>1720</v>
+        <v>1280</v>
       </c>
       <c r="B88">
         <v>0.4107185</v>
@@ -4528,16 +4528,16 @@
         <v>0.74</v>
       </c>
       <c r="E88">
-        <v>0.6328920615745031</v>
+        <v>0.633001041971163</v>
       </c>
       <c r="G88">
         <v>1</v>
       </c>
       <c r="H88">
-        <v>0.975</v>
+        <v>0.995</v>
       </c>
       <c r="I88">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="J88">
         <v>0.5</v>
@@ -4563,28 +4563,28 @@
     </row>
     <row r="89" spans="1:16">
       <c r="A89">
-        <v>1740</v>
+        <v>1380</v>
       </c>
       <c r="B89">
-        <v>0.4107185</v>
+        <v>0.1443065</v>
       </c>
       <c r="C89">
         <v>0.745</v>
       </c>
       <c r="D89">
-        <v>0.74</v>
+        <v>0.26</v>
       </c>
       <c r="E89">
-        <v>0.6317840942084626</v>
+        <v>0.633001041971163</v>
       </c>
       <c r="G89">
         <v>1</v>
       </c>
       <c r="H89">
-        <v>0.97</v>
+        <v>0.995</v>
       </c>
       <c r="I89">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="J89">
         <v>0.5</v>
@@ -4610,28 +4610,28 @@
     </row>
     <row r="90" spans="1:16">
       <c r="A90">
-        <v>1760</v>
+        <v>1440</v>
       </c>
       <c r="B90">
-        <v>0.4107185</v>
+        <v>0.1443065</v>
       </c>
       <c r="C90">
         <v>0.745</v>
       </c>
       <c r="D90">
-        <v>0.74</v>
+        <v>0.26</v>
       </c>
       <c r="E90">
-        <v>0.6350171793093676</v>
+        <v>0.633001041971163</v>
       </c>
       <c r="G90">
         <v>1</v>
       </c>
       <c r="H90">
-        <v>0.98</v>
+        <v>0.995</v>
       </c>
       <c r="I90">
-        <v>0.33</v>
+        <v>0.24</v>
       </c>
       <c r="J90">
         <v>0.5</v>
@@ -4657,28 +4657,28 @@
     </row>
     <row r="91" spans="1:16">
       <c r="A91">
-        <v>1780</v>
+        <v>160</v>
       </c>
       <c r="B91">
-        <v>0.4107185</v>
+        <v>0.06625</v>
       </c>
       <c r="C91">
-        <v>0.745</v>
+        <v>0.5</v>
       </c>
       <c r="D91">
-        <v>0.74</v>
+        <v>0.265</v>
       </c>
       <c r="E91">
-        <v>0.6324016497895343</v>
+        <v>0.633001041971163</v>
       </c>
       <c r="G91">
         <v>1</v>
       </c>
       <c r="H91">
-        <v>0.99</v>
+        <v>0.995</v>
       </c>
       <c r="I91">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="J91">
         <v>0.5</v>
@@ -4704,7 +4704,7 @@
     </row>
     <row r="92" spans="1:16">
       <c r="A92">
-        <v>1800</v>
+        <v>1720</v>
       </c>
       <c r="B92">
         <v>0.4107185</v>
@@ -4716,16 +4716,16 @@
         <v>0.74</v>
       </c>
       <c r="E92">
-        <v>0.6323289961917612</v>
+        <v>0.632892061574503</v>
       </c>
       <c r="G92">
         <v>1</v>
       </c>
       <c r="H92">
-        <v>1</v>
+        <v>0.975</v>
       </c>
       <c r="I92">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="J92">
         <v>0.5</v>
@@ -4751,28 +4751,28 @@
     </row>
     <row r="93" spans="1:16">
       <c r="A93">
-        <v>1820</v>
+        <v>540</v>
       </c>
       <c r="B93">
-        <v>0.4107185</v>
+        <v>0.145114</v>
       </c>
       <c r="C93">
-        <v>0.745</v>
+        <v>0.74</v>
       </c>
       <c r="D93">
-        <v>0.74</v>
+        <v>0.265</v>
       </c>
       <c r="E93">
-        <v>0.6320565452001119</v>
+        <v>0.632746754378957</v>
       </c>
       <c r="G93">
         <v>1</v>
       </c>
       <c r="H93">
-        <v>0.985</v>
+        <v>0.995</v>
       </c>
       <c r="I93">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="J93">
         <v>0.5</v>
@@ -4798,28 +4798,28 @@
     </row>
     <row r="94" spans="1:16">
       <c r="A94">
-        <v>1840</v>
+        <v>380</v>
       </c>
       <c r="B94">
-        <v>0.4107185</v>
+        <v>0.145114</v>
       </c>
       <c r="C94">
-        <v>0.745</v>
+        <v>0.74</v>
       </c>
       <c r="D94">
-        <v>0.74</v>
+        <v>0.265</v>
       </c>
       <c r="E94">
-        <v>0.635035342708811</v>
+        <v>0.63265593738174</v>
       </c>
       <c r="G94">
         <v>1</v>
       </c>
       <c r="H94">
-        <v>0.995</v>
+        <v>0.99</v>
       </c>
       <c r="I94">
-        <v>0.32</v>
+        <v>0.23</v>
       </c>
       <c r="J94">
         <v>0.5</v>
@@ -4845,28 +4845,28 @@
     </row>
     <row r="95" spans="1:16">
       <c r="A95">
-        <v>1860</v>
+        <v>420</v>
       </c>
       <c r="B95">
-        <v>0.4107185</v>
+        <v>0.145114</v>
       </c>
       <c r="C95">
-        <v>0.745</v>
+        <v>0.74</v>
       </c>
       <c r="D95">
-        <v>0.74</v>
+        <v>0.265</v>
       </c>
       <c r="E95">
-        <v>0.6332553295633688</v>
+        <v>0.63265593738174</v>
       </c>
       <c r="G95">
         <v>1</v>
       </c>
       <c r="H95">
-        <v>0.995</v>
+        <v>0.99</v>
       </c>
       <c r="I95">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="J95">
         <v>0.5</v>
@@ -4892,28 +4892,28 @@
     </row>
     <row r="96" spans="1:16">
       <c r="A96">
-        <v>1880</v>
+        <v>140</v>
       </c>
       <c r="B96">
-        <v>0.4107185</v>
+        <v>0.06625</v>
       </c>
       <c r="C96">
-        <v>0.745</v>
+        <v>0.5</v>
       </c>
       <c r="D96">
-        <v>0.74</v>
+        <v>0.265</v>
       </c>
       <c r="E96">
-        <v>0.6335822707533481</v>
+        <v>0.63265593738174</v>
       </c>
       <c r="G96">
         <v>1</v>
       </c>
       <c r="H96">
-        <v>0.985</v>
+        <v>0.99</v>
       </c>
       <c r="I96">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="J96">
         <v>0.5</v>
@@ -4939,34 +4939,34 @@
     </row>
     <row r="97" spans="1:16">
       <c r="A97">
-        <v>1900</v>
+        <v>1360</v>
       </c>
       <c r="B97">
-        <v>0.4107185</v>
+        <v>0.1443065</v>
       </c>
       <c r="C97">
         <v>0.745</v>
       </c>
       <c r="D97">
-        <v>0.74</v>
+        <v>0.26</v>
       </c>
       <c r="E97">
-        <v>0.6204731399284796</v>
+        <v>0.6325651203845239</v>
       </c>
       <c r="G97">
         <v>1</v>
       </c>
       <c r="H97">
-        <v>0.995</v>
+        <v>0.985</v>
       </c>
       <c r="I97">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="J97">
         <v>0.5</v>
       </c>
       <c r="K97">
-        <v>0.2333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="L97">
         <v>1</v>
@@ -4986,19 +4986,19 @@
     </row>
     <row r="98" spans="1:16">
       <c r="A98">
-        <v>1920</v>
+        <v>120</v>
       </c>
       <c r="B98">
-        <v>0.4107185</v>
+        <v>0.06625</v>
       </c>
       <c r="C98">
-        <v>0.745</v>
+        <v>0.5</v>
       </c>
       <c r="D98">
-        <v>0.74</v>
+        <v>0.265</v>
       </c>
       <c r="E98">
-        <v>0.6237498171880487</v>
+        <v>0.6325651203845239</v>
       </c>
       <c r="G98">
         <v>1</v>
@@ -5007,13 +5007,13 @@
         <v>0.985</v>
       </c>
       <c r="I98">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="J98">
         <v>0.5</v>
       </c>
       <c r="K98">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="L98">
         <v>1</v>
@@ -5033,34 +5033,34 @@
     </row>
     <row r="99" spans="1:16">
       <c r="A99">
-        <v>1940</v>
+        <v>400</v>
       </c>
       <c r="B99">
-        <v>0.4107185</v>
+        <v>0.145114</v>
       </c>
       <c r="C99">
-        <v>0.745</v>
+        <v>0.74</v>
       </c>
       <c r="D99">
-        <v>0.74</v>
+        <v>0.265</v>
       </c>
       <c r="E99">
-        <v>0.6172412657208708</v>
+        <v>0.632492466786751</v>
       </c>
       <c r="G99">
         <v>1</v>
       </c>
       <c r="H99">
-        <v>1</v>
+        <v>0.995</v>
       </c>
       <c r="I99">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="J99">
         <v>0.5</v>
       </c>
       <c r="K99">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="L99">
         <v>1</v>
@@ -5080,7 +5080,7 @@
     </row>
     <row r="100" spans="1:16">
       <c r="A100">
-        <v>1960</v>
+        <v>1240</v>
       </c>
       <c r="B100">
         <v>0.4107185</v>
@@ -5092,7 +5092,7 @@
         <v>0.74</v>
       </c>
       <c r="E100">
-        <v>0.6226878637672645</v>
+        <v>0.6324016497895339</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -5101,13 +5101,13 @@
         <v>0.99</v>
       </c>
       <c r="I100">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="J100">
         <v>0.5</v>
       </c>
       <c r="K100">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L100">
         <v>1</v>
@@ -5127,7 +5127,7 @@
     </row>
     <row r="101" spans="1:16">
       <c r="A101">
-        <v>1980</v>
+        <v>1780</v>
       </c>
       <c r="B101">
         <v>0.4107185</v>
@@ -5139,13 +5139,13 @@
         <v>0.74</v>
       </c>
       <c r="E101">
-        <v>0.6192017019674496</v>
+        <v>0.6324016497895339</v>
       </c>
       <c r="G101">
         <v>1</v>
       </c>
       <c r="H101">
-        <v>0.995</v>
+        <v>0.99</v>
       </c>
       <c r="I101">
         <v>0.22</v>
@@ -5154,7 +5154,7 @@
         <v>0.5</v>
       </c>
       <c r="K101">
-        <v>0.2333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="L101">
         <v>1</v>
@@ -5174,34 +5174,34 @@
     </row>
     <row r="102" spans="1:16">
       <c r="A102">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="B102">
-        <v>0.407943375</v>
+        <v>0.4107185</v>
       </c>
       <c r="C102">
         <v>0.745</v>
       </c>
       <c r="D102">
-        <v>0.735</v>
+        <v>0.74</v>
       </c>
       <c r="E102">
-        <v>0.6215350933492638</v>
+        <v>0.632328996191761</v>
       </c>
       <c r="G102">
         <v>1</v>
       </c>
       <c r="H102">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="I102">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="J102">
         <v>0.5</v>
       </c>
       <c r="K102">
-        <v>0.2666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="L102">
         <v>1</v>
@@ -5221,34 +5221,34 @@
     </row>
     <row r="103" spans="1:16">
       <c r="A103">
-        <v>2020</v>
+        <v>460</v>
       </c>
       <c r="B103">
-        <v>0.407943375</v>
+        <v>0.145114</v>
       </c>
       <c r="C103">
-        <v>0.745</v>
+        <v>0.74</v>
       </c>
       <c r="D103">
-        <v>0.735</v>
+        <v>0.265</v>
       </c>
       <c r="E103">
-        <v>0.6202006889368304</v>
+        <v>0.632328996191761</v>
       </c>
       <c r="G103">
         <v>1</v>
       </c>
       <c r="H103">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="I103">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="J103">
         <v>0.5</v>
       </c>
       <c r="K103">
-        <v>0.2333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="L103">
         <v>1</v>
@@ -5268,19 +5268,19 @@
     </row>
     <row r="104" spans="1:16">
       <c r="A104">
-        <v>2040</v>
+        <v>200</v>
       </c>
       <c r="B104">
-        <v>0.407943375</v>
+        <v>0.06625</v>
       </c>
       <c r="C104">
-        <v>0.745</v>
+        <v>0.5</v>
       </c>
       <c r="D104">
-        <v>0.735</v>
+        <v>0.265</v>
       </c>
       <c r="E104">
-        <v>0.6178672975550161</v>
+        <v>0.632310832792318</v>
       </c>
       <c r="G104">
         <v>1</v>
@@ -5289,13 +5289,13 @@
         <v>0.985</v>
       </c>
       <c r="I104">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="J104">
         <v>0.5</v>
       </c>
       <c r="K104">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="L104">
         <v>1</v>
@@ -5315,34 +5315,34 @@
     </row>
     <row r="105" spans="1:16">
       <c r="A105">
-        <v>2060</v>
+        <v>1460</v>
       </c>
       <c r="B105">
-        <v>0.407943375</v>
+        <v>0.1443065</v>
       </c>
       <c r="C105">
         <v>0.745</v>
       </c>
       <c r="D105">
-        <v>0.735</v>
+        <v>0.26</v>
       </c>
       <c r="E105">
-        <v>0.6147988939423968</v>
+        <v>0.6322381791945449</v>
       </c>
       <c r="G105">
         <v>1</v>
       </c>
       <c r="H105">
-        <v>0.985</v>
+        <v>0.995</v>
       </c>
       <c r="I105">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="J105">
         <v>0.5</v>
       </c>
       <c r="K105">
-        <v>0.1333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="L105">
         <v>1</v>
@@ -5362,34 +5362,34 @@
     </row>
     <row r="106" spans="1:16">
       <c r="A106">
-        <v>2080</v>
+        <v>1140</v>
       </c>
       <c r="B106">
-        <v>0.407943375</v>
+        <v>0.1443065</v>
       </c>
       <c r="C106">
         <v>0.745</v>
       </c>
       <c r="D106">
-        <v>0.735</v>
+        <v>0.26</v>
       </c>
       <c r="E106">
-        <v>0.6247669675568727</v>
+        <v>0.632147362197328</v>
       </c>
       <c r="G106">
         <v>1</v>
       </c>
       <c r="H106">
-        <v>0.985</v>
+        <v>0.99</v>
       </c>
       <c r="I106">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="J106">
         <v>0.5</v>
       </c>
       <c r="K106">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="L106">
         <v>1</v>
@@ -5409,34 +5409,34 @@
     </row>
     <row r="107" spans="1:16">
       <c r="A107">
-        <v>2100</v>
+        <v>280</v>
       </c>
       <c r="B107">
-        <v>0.407943375</v>
+        <v>0.145114</v>
       </c>
       <c r="C107">
-        <v>0.745</v>
+        <v>0.74</v>
       </c>
       <c r="D107">
-        <v>0.735</v>
+        <v>0.265</v>
       </c>
       <c r="E107">
-        <v>0.6174773899136335</v>
+        <v>0.6320747085995549</v>
       </c>
       <c r="G107">
         <v>1</v>
       </c>
       <c r="H107">
-        <v>0.985</v>
+        <v>1</v>
       </c>
       <c r="I107">
-        <v>0.29</v>
+        <v>0.2</v>
       </c>
       <c r="J107">
         <v>0.5</v>
       </c>
       <c r="K107">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="L107">
         <v>1</v>
@@ -5456,34 +5456,34 @@
     </row>
     <row r="108" spans="1:16">
       <c r="A108">
-        <v>2120</v>
+        <v>1820</v>
       </c>
       <c r="B108">
-        <v>0.4079666250000001</v>
+        <v>0.4107185</v>
       </c>
       <c r="C108">
-        <v>0.7425</v>
+        <v>0.745</v>
       </c>
       <c r="D108">
         <v>0.74</v>
       </c>
       <c r="E108">
-        <v>0.6203544723854502</v>
+        <v>0.632056545200112</v>
       </c>
       <c r="G108">
         <v>1</v>
       </c>
       <c r="H108">
-        <v>0.995</v>
+        <v>0.985</v>
       </c>
       <c r="I108">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="J108">
         <v>0.5</v>
       </c>
       <c r="K108">
-        <v>0.2666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="L108">
         <v>1</v>
@@ -5503,34 +5503,34 @@
     </row>
     <row r="109" spans="1:16">
       <c r="A109">
-        <v>2140</v>
+        <v>260</v>
       </c>
       <c r="B109">
-        <v>0.4079666250000001</v>
+        <v>0.145114</v>
       </c>
       <c r="C109">
-        <v>0.7425</v>
+        <v>0.74</v>
       </c>
       <c r="D109">
-        <v>0.74</v>
+        <v>0.265</v>
       </c>
       <c r="E109">
-        <v>0.6162967689498199</v>
+        <v>0.631983891602339</v>
       </c>
       <c r="G109">
         <v>1</v>
       </c>
       <c r="H109">
-        <v>0.99</v>
+        <v>0.995</v>
       </c>
       <c r="I109">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="J109">
         <v>0.5</v>
       </c>
       <c r="K109">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -5550,34 +5550,34 @@
     </row>
     <row r="110" spans="1:16">
       <c r="A110">
-        <v>2160</v>
+        <v>1400</v>
       </c>
       <c r="B110">
-        <v>0.4079666250000001</v>
+        <v>0.1443065</v>
       </c>
       <c r="C110">
-        <v>0.7425</v>
+        <v>0.745</v>
       </c>
       <c r="D110">
-        <v>0.74</v>
+        <v>0.26</v>
       </c>
       <c r="E110">
-        <v>0.8047600210049572</v>
+        <v>0.631965728202895</v>
       </c>
       <c r="G110">
         <v>1</v>
       </c>
       <c r="H110">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="I110">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="J110">
         <v>0.5</v>
       </c>
       <c r="K110">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="L110">
         <v>1</v>
@@ -5592,39 +5592,39 @@
         <v>1</v>
       </c>
       <c r="P110">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="111" spans="1:16">
       <c r="A111">
-        <v>2180</v>
+        <v>1220</v>
       </c>
       <c r="B111">
-        <v>0.4079666250000001</v>
+        <v>0.4107185</v>
       </c>
       <c r="C111">
-        <v>0.7425</v>
+        <v>0.745</v>
       </c>
       <c r="D111">
         <v>0.74</v>
       </c>
       <c r="E111">
-        <v>0.8095902743635753</v>
+        <v>0.631893074605122</v>
       </c>
       <c r="G111">
         <v>1</v>
       </c>
       <c r="H111">
-        <v>0.985</v>
+        <v>0.99</v>
       </c>
       <c r="I111">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="J111">
         <v>0.5</v>
       </c>
       <c r="K111">
-        <v>0.2666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="L111">
         <v>1</v>
@@ -5639,39 +5639,39 @@
         <v>1</v>
       </c>
       <c r="P111">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="112" spans="1:16">
       <c r="A112">
-        <v>2200</v>
+        <v>240</v>
       </c>
       <c r="B112">
-        <v>0.4079666250000001</v>
+        <v>0.06625</v>
       </c>
       <c r="C112">
-        <v>0.7425</v>
+        <v>0.5</v>
       </c>
       <c r="D112">
-        <v>0.74</v>
+        <v>0.265</v>
       </c>
       <c r="E112">
-        <v>0.8122869337342552</v>
+        <v>0.631893074605122</v>
       </c>
       <c r="G112">
         <v>1</v>
       </c>
       <c r="H112">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="I112">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J112">
         <v>0.5</v>
       </c>
       <c r="K112">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L112">
         <v>1</v>
@@ -5686,54 +5686,2357 @@
         <v>1</v>
       </c>
       <c r="P112">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="113" spans="1:16">
       <c r="A113">
-        <v>2220</v>
+        <v>1740</v>
       </c>
       <c r="B113">
-        <v>0.4079666250000001</v>
+        <v>0.4107185</v>
       </c>
       <c r="C113">
-        <v>0.7425</v>
+        <v>0.745</v>
       </c>
       <c r="D113">
         <v>0.74</v>
       </c>
       <c r="E113">
-        <v>0.8035164335897401</v>
+        <v>0.631784094208463</v>
       </c>
       <c r="G113">
         <v>1</v>
       </c>
       <c r="H113">
+        <v>0.97</v>
+      </c>
+      <c r="I113">
+        <v>0.21</v>
+      </c>
+      <c r="J113">
+        <v>0.5</v>
+      </c>
+      <c r="K113">
+        <v>0.5</v>
+      </c>
+      <c r="L113">
+        <v>1</v>
+      </c>
+      <c r="M113">
+        <v>0.5</v>
+      </c>
+      <c r="N113">
+        <v>0.5</v>
+      </c>
+      <c r="O113">
+        <v>1</v>
+      </c>
+      <c r="P113">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16">
+      <c r="A114">
+        <v>500</v>
+      </c>
+      <c r="B114">
+        <v>0.145114</v>
+      </c>
+      <c r="C114">
+        <v>0.74</v>
+      </c>
+      <c r="D114">
+        <v>0.265</v>
+      </c>
+      <c r="E114">
+        <v>0.631566133415143</v>
+      </c>
+      <c r="G114">
+        <v>1</v>
+      </c>
+      <c r="H114">
+        <v>1</v>
+      </c>
+      <c r="I114">
+        <v>0.18</v>
+      </c>
+      <c r="J114">
+        <v>0.5</v>
+      </c>
+      <c r="K114">
+        <v>0.5</v>
+      </c>
+      <c r="L114">
+        <v>1</v>
+      </c>
+      <c r="M114">
+        <v>0.5</v>
+      </c>
+      <c r="N114">
+        <v>0.5</v>
+      </c>
+      <c r="O114">
+        <v>1</v>
+      </c>
+      <c r="P114">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16">
+      <c r="A115">
+        <v>560</v>
+      </c>
+      <c r="B115">
+        <v>0.145114</v>
+      </c>
+      <c r="C115">
+        <v>0.74</v>
+      </c>
+      <c r="D115">
+        <v>0.265</v>
+      </c>
+      <c r="E115">
+        <v>0.6315479700157</v>
+      </c>
+      <c r="G115">
+        <v>1</v>
+      </c>
+      <c r="H115">
+        <v>0.985</v>
+      </c>
+      <c r="I115">
+        <v>0.19</v>
+      </c>
+      <c r="J115">
+        <v>0.5</v>
+      </c>
+      <c r="K115">
+        <v>0.5</v>
+      </c>
+      <c r="L115">
+        <v>1</v>
+      </c>
+      <c r="M115">
+        <v>0.5</v>
+      </c>
+      <c r="N115">
+        <v>0.5</v>
+      </c>
+      <c r="O115">
+        <v>1</v>
+      </c>
+      <c r="P115">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16">
+      <c r="A116">
+        <v>1200</v>
+      </c>
+      <c r="B116">
+        <v>0.4107185</v>
+      </c>
+      <c r="C116">
+        <v>0.745</v>
+      </c>
+      <c r="D116">
+        <v>0.74</v>
+      </c>
+      <c r="E116">
+        <v>0.631475316417927</v>
+      </c>
+      <c r="G116">
+        <v>1</v>
+      </c>
+      <c r="H116">
         <v>0.995</v>
       </c>
-      <c r="I113">
+      <c r="I116">
+        <v>0.18</v>
+      </c>
+      <c r="J116">
+        <v>0.5</v>
+      </c>
+      <c r="K116">
+        <v>0.5</v>
+      </c>
+      <c r="L116">
+        <v>1</v>
+      </c>
+      <c r="M116">
+        <v>0.5</v>
+      </c>
+      <c r="N116">
+        <v>0.5</v>
+      </c>
+      <c r="O116">
+        <v>1</v>
+      </c>
+      <c r="P116">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16">
+      <c r="A117">
+        <v>1600</v>
+      </c>
+      <c r="B117">
+        <v>0.4107185</v>
+      </c>
+      <c r="C117">
+        <v>0.745</v>
+      </c>
+      <c r="D117">
+        <v>0.74</v>
+      </c>
+      <c r="E117">
+        <v>0.631311845822937</v>
+      </c>
+      <c r="G117">
+        <v>1</v>
+      </c>
+      <c r="H117">
+        <v>1</v>
+      </c>
+      <c r="I117">
+        <v>0.17</v>
+      </c>
+      <c r="J117">
+        <v>0.5</v>
+      </c>
+      <c r="K117">
+        <v>0.5</v>
+      </c>
+      <c r="L117">
+        <v>1</v>
+      </c>
+      <c r="M117">
+        <v>0.5</v>
+      </c>
+      <c r="N117">
+        <v>0.5</v>
+      </c>
+      <c r="O117">
+        <v>1</v>
+      </c>
+      <c r="P117">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16">
+      <c r="A118">
+        <v>1180</v>
+      </c>
+      <c r="B118">
+        <v>0.4107185</v>
+      </c>
+      <c r="C118">
+        <v>0.745</v>
+      </c>
+      <c r="D118">
+        <v>0.74</v>
+      </c>
+      <c r="E118">
+        <v>0.631130211828504</v>
+      </c>
+      <c r="G118">
+        <v>1</v>
+      </c>
+      <c r="H118">
+        <v>0.99</v>
+      </c>
+      <c r="I118">
+        <v>0.17</v>
+      </c>
+      <c r="J118">
+        <v>0.5</v>
+      </c>
+      <c r="K118">
+        <v>0.5</v>
+      </c>
+      <c r="L118">
+        <v>1</v>
+      </c>
+      <c r="M118">
+        <v>0.5</v>
+      </c>
+      <c r="N118">
+        <v>0.5</v>
+      </c>
+      <c r="O118">
+        <v>1</v>
+      </c>
+      <c r="P118">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16">
+      <c r="A119">
+        <v>2080</v>
+      </c>
+      <c r="B119">
+        <v>0.407943375</v>
+      </c>
+      <c r="C119">
+        <v>0.745</v>
+      </c>
+      <c r="D119">
+        <v>0.735</v>
+      </c>
+      <c r="E119">
+        <v>0.624766967556873</v>
+      </c>
+      <c r="G119">
+        <v>1</v>
+      </c>
+      <c r="H119">
+        <v>0.985</v>
+      </c>
+      <c r="I119">
+        <v>0.25</v>
+      </c>
+      <c r="J119">
+        <v>0.5</v>
+      </c>
+      <c r="K119">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="L119">
+        <v>1</v>
+      </c>
+      <c r="M119">
+        <v>0.5</v>
+      </c>
+      <c r="N119">
+        <v>0.5</v>
+      </c>
+      <c r="O119">
+        <v>1</v>
+      </c>
+      <c r="P119">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16">
+      <c r="A120">
+        <v>1920</v>
+      </c>
+      <c r="B120">
+        <v>0.4107185</v>
+      </c>
+      <c r="C120">
+        <v>0.745</v>
+      </c>
+      <c r="D120">
+        <v>0.74</v>
+      </c>
+      <c r="E120">
+        <v>0.623749817188049</v>
+      </c>
+      <c r="G120">
+        <v>1</v>
+      </c>
+      <c r="H120">
+        <v>0.985</v>
+      </c>
+      <c r="I120">
+        <v>0.21</v>
+      </c>
+      <c r="J120">
+        <v>0.5</v>
+      </c>
+      <c r="K120">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="L120">
+        <v>1</v>
+      </c>
+      <c r="M120">
+        <v>0.5</v>
+      </c>
+      <c r="N120">
+        <v>0.5</v>
+      </c>
+      <c r="O120">
+        <v>1</v>
+      </c>
+      <c r="P120">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16">
+      <c r="A121">
+        <v>1960</v>
+      </c>
+      <c r="B121">
+        <v>0.4107185</v>
+      </c>
+      <c r="C121">
+        <v>0.745</v>
+      </c>
+      <c r="D121">
+        <v>0.74</v>
+      </c>
+      <c r="E121">
+        <v>0.622687863767265</v>
+      </c>
+      <c r="G121">
+        <v>1</v>
+      </c>
+      <c r="H121">
+        <v>0.99</v>
+      </c>
+      <c r="I121">
+        <v>0.23</v>
+      </c>
+      <c r="J121">
+        <v>0.5</v>
+      </c>
+      <c r="K121">
+        <v>0.3</v>
+      </c>
+      <c r="L121">
+        <v>1</v>
+      </c>
+      <c r="M121">
+        <v>0.5</v>
+      </c>
+      <c r="N121">
+        <v>0.5</v>
+      </c>
+      <c r="O121">
+        <v>1</v>
+      </c>
+      <c r="P121">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16">
+      <c r="A122">
+        <v>2000</v>
+      </c>
+      <c r="B122">
+        <v>0.407943375</v>
+      </c>
+      <c r="C122">
+        <v>0.745</v>
+      </c>
+      <c r="D122">
+        <v>0.735</v>
+      </c>
+      <c r="E122">
+        <v>0.621535093349264</v>
+      </c>
+      <c r="G122">
+        <v>1</v>
+      </c>
+      <c r="H122">
+        <v>0.99</v>
+      </c>
+      <c r="I122">
+        <v>0.25</v>
+      </c>
+      <c r="J122">
+        <v>0.5</v>
+      </c>
+      <c r="K122">
+        <v>0.266666666666667</v>
+      </c>
+      <c r="L122">
+        <v>1</v>
+      </c>
+      <c r="M122">
+        <v>0.5</v>
+      </c>
+      <c r="N122">
+        <v>0.5</v>
+      </c>
+      <c r="O122">
+        <v>1</v>
+      </c>
+      <c r="P122">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16">
+      <c r="A123">
+        <v>1100</v>
+      </c>
+      <c r="B123">
+        <v>0.1443065</v>
+      </c>
+      <c r="C123">
+        <v>0.745</v>
+      </c>
+      <c r="D123">
+        <v>0.26</v>
+      </c>
+      <c r="E123">
+        <v>0.620953864567079</v>
+      </c>
+      <c r="G123">
+        <v>1</v>
+      </c>
+      <c r="H123">
+        <v>1</v>
+      </c>
+      <c r="I123">
         <v>0.22</v>
       </c>
-      <c r="J113">
-        <v>0.5</v>
-      </c>
-      <c r="K113">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="L113">
-        <v>1</v>
-      </c>
-      <c r="M113">
-        <v>0.5</v>
-      </c>
-      <c r="N113">
-        <v>0.5</v>
-      </c>
-      <c r="O113">
-        <v>1</v>
-      </c>
-      <c r="P113">
-        <v>1</v>
+      <c r="J123">
+        <v>0.5</v>
+      </c>
+      <c r="K123">
+        <v>0.266666666666667</v>
+      </c>
+      <c r="L123">
+        <v>1</v>
+      </c>
+      <c r="M123">
+        <v>0.5</v>
+      </c>
+      <c r="N123">
+        <v>0.5</v>
+      </c>
+      <c r="O123">
+        <v>1</v>
+      </c>
+      <c r="P123">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16">
+      <c r="A124">
+        <v>1900</v>
+      </c>
+      <c r="B124">
+        <v>0.4107185</v>
+      </c>
+      <c r="C124">
+        <v>0.745</v>
+      </c>
+      <c r="D124">
+        <v>0.74</v>
+      </c>
+      <c r="E124">
+        <v>0.62047313992848</v>
+      </c>
+      <c r="G124">
+        <v>1</v>
+      </c>
+      <c r="H124">
+        <v>0.995</v>
+      </c>
+      <c r="I124">
+        <v>0.27</v>
+      </c>
+      <c r="J124">
+        <v>0.5</v>
+      </c>
+      <c r="K124">
+        <v>0.233333333333333</v>
+      </c>
+      <c r="L124">
+        <v>1</v>
+      </c>
+      <c r="M124">
+        <v>0.5</v>
+      </c>
+      <c r="N124">
+        <v>0.5</v>
+      </c>
+      <c r="O124">
+        <v>1</v>
+      </c>
+      <c r="P124">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16">
+      <c r="A125">
+        <v>2120</v>
+      </c>
+      <c r="B125">
+        <v>0.407966625</v>
+      </c>
+      <c r="C125">
+        <v>0.7425</v>
+      </c>
+      <c r="D125">
+        <v>0.74</v>
+      </c>
+      <c r="E125">
+        <v>0.6203544723854501</v>
+      </c>
+      <c r="G125">
+        <v>1</v>
+      </c>
+      <c r="H125">
+        <v>0.995</v>
+      </c>
+      <c r="I125">
+        <v>0.2</v>
+      </c>
+      <c r="J125">
+        <v>0.5</v>
+      </c>
+      <c r="K125">
+        <v>0.266666666666667</v>
+      </c>
+      <c r="L125">
+        <v>1</v>
+      </c>
+      <c r="M125">
+        <v>0.5</v>
+      </c>
+      <c r="N125">
+        <v>0.5</v>
+      </c>
+      <c r="O125">
+        <v>1</v>
+      </c>
+      <c r="P125">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16">
+      <c r="A126">
+        <v>2020</v>
+      </c>
+      <c r="B126">
+        <v>0.407943375</v>
+      </c>
+      <c r="C126">
+        <v>0.745</v>
+      </c>
+      <c r="D126">
+        <v>0.735</v>
+      </c>
+      <c r="E126">
+        <v>0.62020068893683</v>
+      </c>
+      <c r="G126">
+        <v>1</v>
+      </c>
+      <c r="H126">
+        <v>0.98</v>
+      </c>
+      <c r="I126">
+        <v>0.27</v>
+      </c>
+      <c r="J126">
+        <v>0.5</v>
+      </c>
+      <c r="K126">
+        <v>0.233333333333333</v>
+      </c>
+      <c r="L126">
+        <v>1</v>
+      </c>
+      <c r="M126">
+        <v>0.5</v>
+      </c>
+      <c r="N126">
+        <v>0.5</v>
+      </c>
+      <c r="O126">
+        <v>1</v>
+      </c>
+      <c r="P126">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16">
+      <c r="A127">
+        <v>1980</v>
+      </c>
+      <c r="B127">
+        <v>0.4107185</v>
+      </c>
+      <c r="C127">
+        <v>0.745</v>
+      </c>
+      <c r="D127">
+        <v>0.74</v>
+      </c>
+      <c r="E127">
+        <v>0.6192017019674499</v>
+      </c>
+      <c r="G127">
+        <v>1</v>
+      </c>
+      <c r="H127">
+        <v>0.995</v>
+      </c>
+      <c r="I127">
+        <v>0.22</v>
+      </c>
+      <c r="J127">
+        <v>0.5</v>
+      </c>
+      <c r="K127">
+        <v>0.233333333333333</v>
+      </c>
+      <c r="L127">
+        <v>1</v>
+      </c>
+      <c r="M127">
+        <v>0.5</v>
+      </c>
+      <c r="N127">
+        <v>0.5</v>
+      </c>
+      <c r="O127">
+        <v>1</v>
+      </c>
+      <c r="P127">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16">
+      <c r="A128">
+        <v>1120</v>
+      </c>
+      <c r="B128">
+        <v>0.1443065</v>
+      </c>
+      <c r="C128">
+        <v>0.745</v>
+      </c>
+      <c r="D128">
+        <v>0.26</v>
+      </c>
+      <c r="E128">
+        <v>0.618811794326067</v>
+      </c>
+      <c r="G128">
+        <v>1</v>
+      </c>
+      <c r="H128">
+        <v>0.995</v>
+      </c>
+      <c r="I128">
+        <v>0.27</v>
+      </c>
+      <c r="J128">
+        <v>0.5</v>
+      </c>
+      <c r="K128">
+        <v>0.2</v>
+      </c>
+      <c r="L128">
+        <v>1</v>
+      </c>
+      <c r="M128">
+        <v>0.5</v>
+      </c>
+      <c r="N128">
+        <v>0.5</v>
+      </c>
+      <c r="O128">
+        <v>1</v>
+      </c>
+      <c r="P128">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16">
+      <c r="A129">
+        <v>2040</v>
+      </c>
+      <c r="B129">
+        <v>0.407943375</v>
+      </c>
+      <c r="C129">
+        <v>0.745</v>
+      </c>
+      <c r="D129">
+        <v>0.735</v>
+      </c>
+      <c r="E129">
+        <v>0.617867297555016</v>
+      </c>
+      <c r="G129">
+        <v>1</v>
+      </c>
+      <c r="H129">
+        <v>0.985</v>
+      </c>
+      <c r="I129">
+        <v>0.24</v>
+      </c>
+      <c r="J129">
+        <v>0.5</v>
+      </c>
+      <c r="K129">
+        <v>0.2</v>
+      </c>
+      <c r="L129">
+        <v>1</v>
+      </c>
+      <c r="M129">
+        <v>0.5</v>
+      </c>
+      <c r="N129">
+        <v>0.5</v>
+      </c>
+      <c r="O129">
+        <v>1</v>
+      </c>
+      <c r="P129">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16">
+      <c r="A130">
+        <v>2100</v>
+      </c>
+      <c r="B130">
+        <v>0.407943375</v>
+      </c>
+      <c r="C130">
+        <v>0.745</v>
+      </c>
+      <c r="D130">
+        <v>0.735</v>
+      </c>
+      <c r="E130">
+        <v>0.617477389913634</v>
+      </c>
+      <c r="G130">
+        <v>1</v>
+      </c>
+      <c r="H130">
+        <v>0.985</v>
+      </c>
+      <c r="I130">
+        <v>0.29</v>
+      </c>
+      <c r="J130">
+        <v>0.5</v>
+      </c>
+      <c r="K130">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="L130">
+        <v>1</v>
+      </c>
+      <c r="M130">
+        <v>0.5</v>
+      </c>
+      <c r="N130">
+        <v>0.5</v>
+      </c>
+      <c r="O130">
+        <v>1</v>
+      </c>
+      <c r="P130">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16">
+      <c r="A131">
+        <v>1940</v>
+      </c>
+      <c r="B131">
+        <v>0.4107185</v>
+      </c>
+      <c r="C131">
+        <v>0.745</v>
+      </c>
+      <c r="D131">
+        <v>0.74</v>
+      </c>
+      <c r="E131">
+        <v>0.617241265720871</v>
+      </c>
+      <c r="G131">
+        <v>1</v>
+      </c>
+      <c r="H131">
+        <v>1</v>
+      </c>
+      <c r="I131">
+        <v>0.27</v>
+      </c>
+      <c r="J131">
+        <v>0.5</v>
+      </c>
+      <c r="K131">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="L131">
+        <v>1</v>
+      </c>
+      <c r="M131">
+        <v>0.5</v>
+      </c>
+      <c r="N131">
+        <v>0.5</v>
+      </c>
+      <c r="O131">
+        <v>1</v>
+      </c>
+      <c r="P131">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16">
+      <c r="A132">
+        <v>2140</v>
+      </c>
+      <c r="B132">
+        <v>0.407966625</v>
+      </c>
+      <c r="C132">
+        <v>0.7425</v>
+      </c>
+      <c r="D132">
+        <v>0.74</v>
+      </c>
+      <c r="E132">
+        <v>0.61629676894982</v>
+      </c>
+      <c r="G132">
+        <v>1</v>
+      </c>
+      <c r="H132">
+        <v>0.99</v>
+      </c>
+      <c r="I132">
+        <v>0.24</v>
+      </c>
+      <c r="J132">
+        <v>0.5</v>
+      </c>
+      <c r="K132">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="L132">
+        <v>1</v>
+      </c>
+      <c r="M132">
+        <v>0.5</v>
+      </c>
+      <c r="N132">
+        <v>0.5</v>
+      </c>
+      <c r="O132">
+        <v>1</v>
+      </c>
+      <c r="P132">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16">
+      <c r="A133">
+        <v>2060</v>
+      </c>
+      <c r="B133">
+        <v>0.407943375</v>
+      </c>
+      <c r="C133">
+        <v>0.745</v>
+      </c>
+      <c r="D133">
+        <v>0.735</v>
+      </c>
+      <c r="E133">
+        <v>0.614798893942397</v>
+      </c>
+      <c r="G133">
+        <v>1</v>
+      </c>
+      <c r="H133">
+        <v>0.985</v>
+      </c>
+      <c r="I133">
+        <v>0.25</v>
+      </c>
+      <c r="J133">
+        <v>0.5</v>
+      </c>
+      <c r="K133">
+        <v>0.133333333333333</v>
+      </c>
+      <c r="L133">
+        <v>1</v>
+      </c>
+      <c r="M133">
+        <v>0.5</v>
+      </c>
+      <c r="N133">
+        <v>0.5</v>
+      </c>
+      <c r="O133">
+        <v>1</v>
+      </c>
+      <c r="P133">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16">
+      <c r="A134">
+        <v>960</v>
+      </c>
+      <c r="B134">
+        <v>0.0051005</v>
+      </c>
+      <c r="C134">
+        <v>0.505</v>
+      </c>
+      <c r="D134">
+        <v>0.02</v>
+      </c>
+      <c r="E134">
+        <v>0.606756615339082</v>
+      </c>
+      <c r="G134">
+        <v>1</v>
+      </c>
+      <c r="H134">
+        <v>1</v>
+      </c>
+      <c r="I134">
+        <v>0.28</v>
+      </c>
+      <c r="J134">
+        <v>0.5</v>
+      </c>
+      <c r="K134">
+        <v>0.5</v>
+      </c>
+      <c r="L134">
+        <v>1</v>
+      </c>
+      <c r="M134">
+        <v>0.5</v>
+      </c>
+      <c r="N134">
+        <v>1</v>
+      </c>
+      <c r="O134">
+        <v>0.5</v>
+      </c>
+      <c r="P134">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16">
+      <c r="A135">
+        <v>860</v>
+      </c>
+      <c r="B135">
+        <v>0.003825375</v>
+      </c>
+      <c r="C135">
+        <v>0.505</v>
+      </c>
+      <c r="D135">
+        <v>0.015</v>
+      </c>
+      <c r="E135">
+        <v>0.606665798341865</v>
+      </c>
+      <c r="G135">
+        <v>1</v>
+      </c>
+      <c r="H135">
+        <v>0.995</v>
+      </c>
+      <c r="I135">
+        <v>0.28</v>
+      </c>
+      <c r="J135">
+        <v>0.5</v>
+      </c>
+      <c r="K135">
+        <v>0.5</v>
+      </c>
+      <c r="L135">
+        <v>1</v>
+      </c>
+      <c r="M135">
+        <v>0.5</v>
+      </c>
+      <c r="N135">
+        <v>1</v>
+      </c>
+      <c r="O135">
+        <v>0.5</v>
+      </c>
+      <c r="P135">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16">
+      <c r="A136">
+        <v>800</v>
+      </c>
+      <c r="B136">
+        <v>0.003825375</v>
+      </c>
+      <c r="C136">
+        <v>0.505</v>
+      </c>
+      <c r="D136">
+        <v>0.015</v>
+      </c>
+      <c r="E136">
+        <v>0.606574981344649</v>
+      </c>
+      <c r="G136">
+        <v>1</v>
+      </c>
+      <c r="H136">
+        <v>0.99</v>
+      </c>
+      <c r="I136">
+        <v>0.28</v>
+      </c>
+      <c r="J136">
+        <v>0.5</v>
+      </c>
+      <c r="K136">
+        <v>0.5</v>
+      </c>
+      <c r="L136">
+        <v>1</v>
+      </c>
+      <c r="M136">
+        <v>0.5</v>
+      </c>
+      <c r="N136">
+        <v>1</v>
+      </c>
+      <c r="O136">
+        <v>0.5</v>
+      </c>
+      <c r="P136">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16">
+      <c r="A137">
+        <v>780</v>
+      </c>
+      <c r="B137">
+        <v>0.0051005</v>
+      </c>
+      <c r="C137">
+        <v>0.505</v>
+      </c>
+      <c r="D137">
+        <v>0.02</v>
+      </c>
+      <c r="E137">
+        <v>0.606320693752443</v>
+      </c>
+      <c r="G137">
+        <v>1</v>
+      </c>
+      <c r="H137">
+        <v>0.99</v>
+      </c>
+      <c r="I137">
+        <v>0.27</v>
+      </c>
+      <c r="J137">
+        <v>0.5</v>
+      </c>
+      <c r="K137">
+        <v>0.5</v>
+      </c>
+      <c r="L137">
+        <v>1</v>
+      </c>
+      <c r="M137">
+        <v>0.5</v>
+      </c>
+      <c r="N137">
+        <v>1</v>
+      </c>
+      <c r="O137">
+        <v>0.5</v>
+      </c>
+      <c r="P137">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16">
+      <c r="A138">
+        <v>720</v>
+      </c>
+      <c r="B138">
+        <v>0.003825375</v>
+      </c>
+      <c r="C138">
+        <v>0.505</v>
+      </c>
+      <c r="D138">
+        <v>0.015</v>
+      </c>
+      <c r="E138">
+        <v>0.606229876755226</v>
+      </c>
+      <c r="G138">
+        <v>1</v>
+      </c>
+      <c r="H138">
+        <v>0.985</v>
+      </c>
+      <c r="I138">
+        <v>0.27</v>
+      </c>
+      <c r="J138">
+        <v>0.5</v>
+      </c>
+      <c r="K138">
+        <v>0.5</v>
+      </c>
+      <c r="L138">
+        <v>1</v>
+      </c>
+      <c r="M138">
+        <v>0.5</v>
+      </c>
+      <c r="N138">
+        <v>1</v>
+      </c>
+      <c r="O138">
+        <v>0.5</v>
+      </c>
+      <c r="P138">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16">
+      <c r="A139">
+        <v>760</v>
+      </c>
+      <c r="B139">
+        <v>0.0051005</v>
+      </c>
+      <c r="C139">
+        <v>0.505</v>
+      </c>
+      <c r="D139">
+        <v>0.02</v>
+      </c>
+      <c r="E139">
+        <v>0.606066406160237</v>
+      </c>
+      <c r="G139">
+        <v>1</v>
+      </c>
+      <c r="H139">
+        <v>0.99</v>
+      </c>
+      <c r="I139">
+        <v>0.26</v>
+      </c>
+      <c r="J139">
+        <v>0.5</v>
+      </c>
+      <c r="K139">
+        <v>0.5</v>
+      </c>
+      <c r="L139">
+        <v>1</v>
+      </c>
+      <c r="M139">
+        <v>0.5</v>
+      </c>
+      <c r="N139">
+        <v>1</v>
+      </c>
+      <c r="O139">
+        <v>0.5</v>
+      </c>
+      <c r="P139">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16">
+      <c r="A140">
+        <v>840</v>
+      </c>
+      <c r="B140">
+        <v>0.003825375</v>
+      </c>
+      <c r="C140">
+        <v>0.505</v>
+      </c>
+      <c r="D140">
+        <v>0.015</v>
+      </c>
+      <c r="E140">
+        <v>0.606066406160237</v>
+      </c>
+      <c r="G140">
+        <v>1</v>
+      </c>
+      <c r="H140">
+        <v>0.99</v>
+      </c>
+      <c r="I140">
+        <v>0.26</v>
+      </c>
+      <c r="J140">
+        <v>0.5</v>
+      </c>
+      <c r="K140">
+        <v>0.5</v>
+      </c>
+      <c r="L140">
+        <v>1</v>
+      </c>
+      <c r="M140">
+        <v>0.5</v>
+      </c>
+      <c r="N140">
+        <v>1</v>
+      </c>
+      <c r="O140">
+        <v>0.5</v>
+      </c>
+      <c r="P140">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16">
+      <c r="A141">
+        <v>1000</v>
+      </c>
+      <c r="B141">
+        <v>0.0051005</v>
+      </c>
+      <c r="C141">
+        <v>0.505</v>
+      </c>
+      <c r="D141">
+        <v>0.02</v>
+      </c>
+      <c r="E141">
+        <v>0.60597558916302</v>
+      </c>
+      <c r="G141">
+        <v>1</v>
+      </c>
+      <c r="H141">
+        <v>0.985</v>
+      </c>
+      <c r="I141">
+        <v>0.26</v>
+      </c>
+      <c r="J141">
+        <v>0.5</v>
+      </c>
+      <c r="K141">
+        <v>0.5</v>
+      </c>
+      <c r="L141">
+        <v>1</v>
+      </c>
+      <c r="M141">
+        <v>0.5</v>
+      </c>
+      <c r="N141">
+        <v>1</v>
+      </c>
+      <c r="O141">
+        <v>0.5</v>
+      </c>
+      <c r="P141">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16">
+      <c r="A142">
+        <v>1080</v>
+      </c>
+      <c r="B142">
+        <v>0.0051005</v>
+      </c>
+      <c r="C142">
+        <v>0.505</v>
+      </c>
+      <c r="D142">
+        <v>0.02</v>
+      </c>
+      <c r="E142">
+        <v>0.60597558916302</v>
+      </c>
+      <c r="G142">
+        <v>1</v>
+      </c>
+      <c r="H142">
+        <v>0.985</v>
+      </c>
+      <c r="I142">
+        <v>0.26</v>
+      </c>
+      <c r="J142">
+        <v>0.5</v>
+      </c>
+      <c r="K142">
+        <v>0.5</v>
+      </c>
+      <c r="L142">
+        <v>1</v>
+      </c>
+      <c r="M142">
+        <v>0.5</v>
+      </c>
+      <c r="N142">
+        <v>1</v>
+      </c>
+      <c r="O142">
+        <v>0.5</v>
+      </c>
+      <c r="P142">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16">
+      <c r="A143">
+        <v>660</v>
+      </c>
+      <c r="B143">
+        <v>0.003825375</v>
+      </c>
+      <c r="C143">
+        <v>0.505</v>
+      </c>
+      <c r="D143">
+        <v>0.015</v>
+      </c>
+      <c r="E143">
+        <v>0.605902935565247</v>
+      </c>
+      <c r="G143">
+        <v>1</v>
+      </c>
+      <c r="H143">
+        <v>0.995</v>
+      </c>
+      <c r="I143">
+        <v>0.25</v>
+      </c>
+      <c r="J143">
+        <v>0.5</v>
+      </c>
+      <c r="K143">
+        <v>0.5</v>
+      </c>
+      <c r="L143">
+        <v>1</v>
+      </c>
+      <c r="M143">
+        <v>0.5</v>
+      </c>
+      <c r="N143">
+        <v>1</v>
+      </c>
+      <c r="O143">
+        <v>0.5</v>
+      </c>
+      <c r="P143">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16">
+      <c r="A144">
+        <v>740</v>
+      </c>
+      <c r="B144">
+        <v>0.003825375</v>
+      </c>
+      <c r="C144">
+        <v>0.505</v>
+      </c>
+      <c r="D144">
+        <v>0.015</v>
+      </c>
+      <c r="E144">
+        <v>0.605902935565247</v>
+      </c>
+      <c r="G144">
+        <v>1</v>
+      </c>
+      <c r="H144">
+        <v>0.995</v>
+      </c>
+      <c r="I144">
+        <v>0.25</v>
+      </c>
+      <c r="J144">
+        <v>0.5</v>
+      </c>
+      <c r="K144">
+        <v>0.5</v>
+      </c>
+      <c r="L144">
+        <v>1</v>
+      </c>
+      <c r="M144">
+        <v>0.5</v>
+      </c>
+      <c r="N144">
+        <v>1</v>
+      </c>
+      <c r="O144">
+        <v>0.5</v>
+      </c>
+      <c r="P144">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16">
+      <c r="A145">
+        <v>1040</v>
+      </c>
+      <c r="B145">
+        <v>0.0051005</v>
+      </c>
+      <c r="C145">
+        <v>0.505</v>
+      </c>
+      <c r="D145">
+        <v>0.02</v>
+      </c>
+      <c r="E145">
+        <v>0.605812118568031</v>
+      </c>
+      <c r="G145">
+        <v>1</v>
+      </c>
+      <c r="H145">
+        <v>0.99</v>
+      </c>
+      <c r="I145">
+        <v>0.25</v>
+      </c>
+      <c r="J145">
+        <v>0.5</v>
+      </c>
+      <c r="K145">
+        <v>0.5</v>
+      </c>
+      <c r="L145">
+        <v>1</v>
+      </c>
+      <c r="M145">
+        <v>0.5</v>
+      </c>
+      <c r="N145">
+        <v>1</v>
+      </c>
+      <c r="O145">
+        <v>0.5</v>
+      </c>
+      <c r="P145">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16">
+      <c r="A146">
+        <v>680</v>
+      </c>
+      <c r="B146">
+        <v>0.003825375</v>
+      </c>
+      <c r="C146">
+        <v>0.505</v>
+      </c>
+      <c r="D146">
+        <v>0.015</v>
+      </c>
+      <c r="E146">
+        <v>0.6057213015708141</v>
+      </c>
+      <c r="G146">
+        <v>1</v>
+      </c>
+      <c r="H146">
+        <v>0.985</v>
+      </c>
+      <c r="I146">
+        <v>0.25</v>
+      </c>
+      <c r="J146">
+        <v>0.5</v>
+      </c>
+      <c r="K146">
+        <v>0.5</v>
+      </c>
+      <c r="L146">
+        <v>1</v>
+      </c>
+      <c r="M146">
+        <v>0.5</v>
+      </c>
+      <c r="N146">
+        <v>1</v>
+      </c>
+      <c r="O146">
+        <v>0.5</v>
+      </c>
+      <c r="P146">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16">
+      <c r="A147">
+        <v>920</v>
+      </c>
+      <c r="B147">
+        <v>0.003825375</v>
+      </c>
+      <c r="C147">
+        <v>0.505</v>
+      </c>
+      <c r="D147">
+        <v>0.015</v>
+      </c>
+      <c r="E147">
+        <v>0.605648647973041</v>
+      </c>
+      <c r="G147">
+        <v>1</v>
+      </c>
+      <c r="H147">
+        <v>0.995</v>
+      </c>
+      <c r="I147">
+        <v>0.24</v>
+      </c>
+      <c r="J147">
+        <v>0.5</v>
+      </c>
+      <c r="K147">
+        <v>0.5</v>
+      </c>
+      <c r="L147">
+        <v>1</v>
+      </c>
+      <c r="M147">
+        <v>0.5</v>
+      </c>
+      <c r="N147">
+        <v>1</v>
+      </c>
+      <c r="O147">
+        <v>0.5</v>
+      </c>
+      <c r="P147">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16">
+      <c r="A148">
+        <v>900</v>
+      </c>
+      <c r="B148">
+        <v>0.003825375</v>
+      </c>
+      <c r="C148">
+        <v>0.505</v>
+      </c>
+      <c r="D148">
+        <v>0.015</v>
+      </c>
+      <c r="E148">
+        <v>0.6053943603808351</v>
+      </c>
+      <c r="G148">
+        <v>1</v>
+      </c>
+      <c r="H148">
+        <v>0.995</v>
+      </c>
+      <c r="I148">
+        <v>0.23</v>
+      </c>
+      <c r="J148">
+        <v>0.5</v>
+      </c>
+      <c r="K148">
+        <v>0.5</v>
+      </c>
+      <c r="L148">
+        <v>1</v>
+      </c>
+      <c r="M148">
+        <v>0.5</v>
+      </c>
+      <c r="N148">
+        <v>1</v>
+      </c>
+      <c r="O148">
+        <v>0.5</v>
+      </c>
+      <c r="P148">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16">
+      <c r="A149">
+        <v>700</v>
+      </c>
+      <c r="B149">
+        <v>0.003825375</v>
+      </c>
+      <c r="C149">
+        <v>0.505</v>
+      </c>
+      <c r="D149">
+        <v>0.015</v>
+      </c>
+      <c r="E149">
+        <v>0.605303543383619</v>
+      </c>
+      <c r="G149">
+        <v>1</v>
+      </c>
+      <c r="H149">
+        <v>0.99</v>
+      </c>
+      <c r="I149">
+        <v>0.23</v>
+      </c>
+      <c r="J149">
+        <v>0.5</v>
+      </c>
+      <c r="K149">
+        <v>0.5</v>
+      </c>
+      <c r="L149">
+        <v>1</v>
+      </c>
+      <c r="M149">
+        <v>0.5</v>
+      </c>
+      <c r="N149">
+        <v>1</v>
+      </c>
+      <c r="O149">
+        <v>0.5</v>
+      </c>
+      <c r="P149">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16">
+      <c r="A150">
+        <v>880</v>
+      </c>
+      <c r="B150">
+        <v>0.003825375</v>
+      </c>
+      <c r="C150">
+        <v>0.505</v>
+      </c>
+      <c r="D150">
+        <v>0.015</v>
+      </c>
+      <c r="E150">
+        <v>0.605303543383619</v>
+      </c>
+      <c r="G150">
+        <v>1</v>
+      </c>
+      <c r="H150">
+        <v>0.99</v>
+      </c>
+      <c r="I150">
+        <v>0.23</v>
+      </c>
+      <c r="J150">
+        <v>0.5</v>
+      </c>
+      <c r="K150">
+        <v>0.5</v>
+      </c>
+      <c r="L150">
+        <v>1</v>
+      </c>
+      <c r="M150">
+        <v>0.5</v>
+      </c>
+      <c r="N150">
+        <v>1</v>
+      </c>
+      <c r="O150">
+        <v>0.5</v>
+      </c>
+      <c r="P150">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16">
+      <c r="A151">
+        <v>1020</v>
+      </c>
+      <c r="B151">
+        <v>0.0051005</v>
+      </c>
+      <c r="C151">
+        <v>0.505</v>
+      </c>
+      <c r="D151">
+        <v>0.02</v>
+      </c>
+      <c r="E151">
+        <v>0.605049255791413</v>
+      </c>
+      <c r="G151">
+        <v>1</v>
+      </c>
+      <c r="H151">
+        <v>0.99</v>
+      </c>
+      <c r="I151">
+        <v>0.22</v>
+      </c>
+      <c r="J151">
+        <v>0.5</v>
+      </c>
+      <c r="K151">
+        <v>0.5</v>
+      </c>
+      <c r="L151">
+        <v>1</v>
+      </c>
+      <c r="M151">
+        <v>0.5</v>
+      </c>
+      <c r="N151">
+        <v>1</v>
+      </c>
+      <c r="O151">
+        <v>0.5</v>
+      </c>
+      <c r="P151">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16">
+      <c r="A152">
+        <v>1060</v>
+      </c>
+      <c r="B152">
+        <v>0.0051005</v>
+      </c>
+      <c r="C152">
+        <v>0.505</v>
+      </c>
+      <c r="D152">
+        <v>0.02</v>
+      </c>
+      <c r="E152">
+        <v>0.604958438794196</v>
+      </c>
+      <c r="G152">
+        <v>1</v>
+      </c>
+      <c r="H152">
+        <v>0.985</v>
+      </c>
+      <c r="I152">
+        <v>0.22</v>
+      </c>
+      <c r="J152">
+        <v>0.5</v>
+      </c>
+      <c r="K152">
+        <v>0.5</v>
+      </c>
+      <c r="L152">
+        <v>1</v>
+      </c>
+      <c r="M152">
+        <v>0.5</v>
+      </c>
+      <c r="N152">
+        <v>1</v>
+      </c>
+      <c r="O152">
+        <v>0.5</v>
+      </c>
+      <c r="P152">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16">
+      <c r="A153">
+        <v>820</v>
+      </c>
+      <c r="B153">
+        <v>0.003825375</v>
+      </c>
+      <c r="C153">
+        <v>0.505</v>
+      </c>
+      <c r="D153">
+        <v>0.015</v>
+      </c>
+      <c r="E153">
+        <v>0.604958438794196</v>
+      </c>
+      <c r="G153">
+        <v>1</v>
+      </c>
+      <c r="H153">
+        <v>0.985</v>
+      </c>
+      <c r="I153">
+        <v>0.22</v>
+      </c>
+      <c r="J153">
+        <v>0.5</v>
+      </c>
+      <c r="K153">
+        <v>0.5</v>
+      </c>
+      <c r="L153">
+        <v>1</v>
+      </c>
+      <c r="M153">
+        <v>0.5</v>
+      </c>
+      <c r="N153">
+        <v>1</v>
+      </c>
+      <c r="O153">
+        <v>0.5</v>
+      </c>
+      <c r="P153">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16">
+      <c r="A154">
+        <v>940</v>
+      </c>
+      <c r="B154">
+        <v>0.0051005</v>
+      </c>
+      <c r="C154">
+        <v>0.505</v>
+      </c>
+      <c r="D154">
+        <v>0.02</v>
+      </c>
+      <c r="E154">
+        <v>0.604359046612568</v>
+      </c>
+      <c r="G154">
+        <v>1</v>
+      </c>
+      <c r="H154">
+        <v>0.98</v>
+      </c>
+      <c r="I154">
+        <v>0.2</v>
+      </c>
+      <c r="J154">
+        <v>0.5</v>
+      </c>
+      <c r="K154">
+        <v>0.5</v>
+      </c>
+      <c r="L154">
+        <v>1</v>
+      </c>
+      <c r="M154">
+        <v>0.5</v>
+      </c>
+      <c r="N154">
+        <v>1</v>
+      </c>
+      <c r="O154">
+        <v>0.5</v>
+      </c>
+      <c r="P154">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16">
+      <c r="A155">
+        <v>980</v>
+      </c>
+      <c r="B155">
+        <v>0.0051005</v>
+      </c>
+      <c r="C155">
+        <v>0.505</v>
+      </c>
+      <c r="D155">
+        <v>0.02</v>
+      </c>
+      <c r="E155">
+        <v>0.603868634827599</v>
+      </c>
+      <c r="G155">
+        <v>1</v>
+      </c>
+      <c r="H155">
+        <v>0.995</v>
+      </c>
+      <c r="I155">
+        <v>0.17</v>
+      </c>
+      <c r="J155">
+        <v>0.5</v>
+      </c>
+      <c r="K155">
+        <v>0.5</v>
+      </c>
+      <c r="L155">
+        <v>1</v>
+      </c>
+      <c r="M155">
+        <v>0.5</v>
+      </c>
+      <c r="N155">
+        <v>1</v>
+      </c>
+      <c r="O155">
+        <v>0.5</v>
+      </c>
+      <c r="P155">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16">
+      <c r="A156">
+        <v>3080</v>
+      </c>
+      <c r="B156">
+        <v>0.128787625</v>
+      </c>
+      <c r="C156">
+        <v>0.505</v>
+      </c>
+      <c r="D156">
+        <v>0.505</v>
+      </c>
+      <c r="E156">
+        <v>0.601489229500528</v>
+      </c>
+      <c r="G156">
+        <v>1</v>
+      </c>
+      <c r="H156">
+        <v>0.99</v>
+      </c>
+      <c r="I156">
+        <v>0.22</v>
+      </c>
+      <c r="J156">
+        <v>0.4</v>
+      </c>
+      <c r="K156">
+        <v>0.5</v>
+      </c>
+      <c r="L156">
+        <v>1</v>
+      </c>
+      <c r="M156">
+        <v>0.5</v>
+      </c>
+      <c r="N156">
+        <v>1</v>
+      </c>
+      <c r="O156">
+        <v>0.5</v>
+      </c>
+      <c r="P156">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16">
+      <c r="A157">
+        <v>3160</v>
+      </c>
+      <c r="B157">
+        <v>0.006375625</v>
+      </c>
+      <c r="C157">
+        <v>0.505</v>
+      </c>
+      <c r="D157">
+        <v>0.025</v>
+      </c>
+      <c r="E157">
+        <v>0.598855536581252</v>
+      </c>
+      <c r="G157">
+        <v>1</v>
+      </c>
+      <c r="H157">
+        <v>0.985</v>
+      </c>
+      <c r="I157">
+        <v>0.26</v>
+      </c>
+      <c r="J157">
+        <v>0.3</v>
+      </c>
+      <c r="K157">
+        <v>0.5</v>
+      </c>
+      <c r="L157">
+        <v>1</v>
+      </c>
+      <c r="M157">
+        <v>0.5</v>
+      </c>
+      <c r="N157">
+        <v>1</v>
+      </c>
+      <c r="O157">
+        <v>0.5</v>
+      </c>
+      <c r="P157">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16">
+      <c r="A158">
+        <v>3120</v>
+      </c>
+      <c r="B158">
+        <v>0.128787625</v>
+      </c>
+      <c r="C158">
+        <v>0.505</v>
+      </c>
+      <c r="D158">
+        <v>0.505</v>
+      </c>
+      <c r="E158">
+        <v>0.597329811028016</v>
+      </c>
+      <c r="G158">
+        <v>1</v>
+      </c>
+      <c r="H158">
+        <v>0.985</v>
+      </c>
+      <c r="I158">
+        <v>0.2</v>
+      </c>
+      <c r="J158">
+        <v>0.3</v>
+      </c>
+      <c r="K158">
+        <v>0.5</v>
+      </c>
+      <c r="L158">
+        <v>1</v>
+      </c>
+      <c r="M158">
+        <v>0.5</v>
+      </c>
+      <c r="N158">
+        <v>1</v>
+      </c>
+      <c r="O158">
+        <v>0.5</v>
+      </c>
+      <c r="P158">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16">
+      <c r="A159">
+        <v>3140</v>
+      </c>
+      <c r="B159">
+        <v>0.128787625</v>
+      </c>
+      <c r="C159">
+        <v>0.505</v>
+      </c>
+      <c r="D159">
+        <v>0.505</v>
+      </c>
+      <c r="E159">
+        <v>0.594805098505399</v>
+      </c>
+      <c r="G159">
+        <v>1</v>
+      </c>
+      <c r="H159">
+        <v>1</v>
+      </c>
+      <c r="I159">
+        <v>0.23</v>
+      </c>
+      <c r="J159">
+        <v>0.2</v>
+      </c>
+      <c r="K159">
+        <v>0.5</v>
+      </c>
+      <c r="L159">
+        <v>1</v>
+      </c>
+      <c r="M159">
+        <v>0.5</v>
+      </c>
+      <c r="N159">
+        <v>1</v>
+      </c>
+      <c r="O159">
+        <v>0.5</v>
+      </c>
+      <c r="P159">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16">
+      <c r="A160">
+        <v>3100</v>
+      </c>
+      <c r="B160">
+        <v>0.128787625</v>
+      </c>
+      <c r="C160">
+        <v>0.505</v>
+      </c>
+      <c r="D160">
+        <v>0.505</v>
+      </c>
+      <c r="E160">
+        <v>0.590809150627876</v>
+      </c>
+      <c r="G160">
+        <v>1</v>
+      </c>
+      <c r="H160">
+        <v>0.99</v>
+      </c>
+      <c r="I160">
+        <v>0.22</v>
+      </c>
+      <c r="J160">
+        <v>0.1</v>
+      </c>
+      <c r="K160">
+        <v>0.5</v>
+      </c>
+      <c r="L160">
+        <v>1</v>
+      </c>
+      <c r="M160">
+        <v>0.5</v>
+      </c>
+      <c r="N160">
+        <v>1</v>
+      </c>
+      <c r="O160">
+        <v>0.5</v>
+      </c>
+      <c r="P160">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16">
+      <c r="A161">
+        <v>3180</v>
+      </c>
+      <c r="B161">
+        <v>0.006375625</v>
+      </c>
+      <c r="C161">
+        <v>0.505</v>
+      </c>
+      <c r="D161">
+        <v>0.025</v>
+      </c>
+      <c r="E161">
+        <v>0.5912051127357392</v>
+      </c>
+      <c r="G161">
+        <v>1</v>
+      </c>
+      <c r="H161">
+        <v>0.995</v>
+      </c>
+      <c r="I161">
+        <v>0.26</v>
+      </c>
+      <c r="J161">
+        <v>0.5</v>
+      </c>
+      <c r="K161">
+        <v>0.2</v>
+      </c>
+      <c r="L161">
+        <v>1</v>
+      </c>
+      <c r="M161">
+        <v>0.5</v>
+      </c>
+      <c r="N161">
+        <v>1</v>
+      </c>
+      <c r="O161">
+        <v>0.5</v>
+      </c>
+      <c r="P161">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16">
+      <c r="A162">
+        <v>3200</v>
+      </c>
+      <c r="B162">
+        <v>0.006375625</v>
+      </c>
+      <c r="C162">
+        <v>0.505</v>
+      </c>
+      <c r="D162">
+        <v>0.025</v>
+      </c>
+      <c r="E162">
+        <v>0.5936741241667299</v>
+      </c>
+      <c r="G162">
+        <v>1</v>
+      </c>
+      <c r="H162">
+        <v>0.99</v>
+      </c>
+      <c r="I162">
+        <v>0.23</v>
+      </c>
+      <c r="J162">
+        <v>0.5</v>
+      </c>
+      <c r="K162">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="L162">
+        <v>1</v>
+      </c>
+      <c r="M162">
+        <v>0.5</v>
+      </c>
+      <c r="N162">
+        <v>1</v>
+      </c>
+      <c r="O162">
+        <v>0.5</v>
+      </c>
+      <c r="P162">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
